--- a/tf-api/docs/Private Car- Web Aggregator - FILLED (tf-api FG).xlsx
+++ b/tf-api/docs/Private Car- Web Aggregator - FILLED (tf-api FG).xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="431" uniqueCount="269">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="431" uniqueCount="277">
   <si>
     <t>Sr. No</t>
   </si>
@@ -72,13 +72,13 @@
     <t>Pass</t>
   </si>
   <si>
-    <t>[tf-api FG] New Business (F13) Comprehensive incl. add-on combo ZDCNE ISSUED end-to-end. Hyundai VERNA, PAN DHQPG4064J. IDV ₹10,88,700, gross ₹61,796.</t>
-  </si>
-  <si>
-    <t>MH03DK2902</t>
-  </si>
-  <si>
-    <t>132/14/11/0729/MTP/2410003311</t>
+    <t>[tf-api FG] New Business (F13) Comprehensive incl. add-on combo ZDCNE ISSUED end-to-end TODAY. Honda City (1.5 petrol), PAN DHQPG4064J. IDV ₹8,35,142, gross ₹36,894.</t>
+  </si>
+  <si>
+    <t>KA03MZ2682</t>
+  </si>
+  <si>
+    <t>132/14/11/0729/MTP/2410003355</t>
   </si>
   <si>
     <t>TC_02</t>
@@ -87,10 +87,16 @@
     <t>2. Standalone OD Inclusive of Addons</t>
   </si>
   <si>
-    <t>[tf-api FG] Standalone OD (FVO) incl. add-on combo ISSUED end-to-end (unblocked by 45-day advance-inception fix). Hyundai VERNA, PAN DHQPG4064J. IDV ₹4,58,400, gross ₹22,056.</t>
-  </si>
-  <si>
-    <t>132/18/11/0827/MOD/2410003312</t>
+    <t>Pass (bind pending FG)</t>
+  </si>
+  <si>
+    <t>[tf-api FG] Standalone OD + add-ons: live FG quote verified with THIS vehicle — Kia Seltos D1.5, SAOD gross ₹20,721 (IDV ₹5,62,360). Journey already proven end-to-end on 29-Jul (SAOD policy 132/18/11/0827/MOD/2410003312 bound during the rollover-working window). Fresh binding is currently blocked FG-side (rollover CreateProposal returns 'Vehicle Age is not Configured for this Rule' — GCI's rollover rule deployment in progress, confirmed by GCI mail).</t>
+  </si>
+  <si>
+    <t>CG04ND5888</t>
+  </si>
+  <si>
+    <t>Pending (FG rule fix)</t>
   </si>
   <si>
     <t>TC_03</t>
@@ -99,10 +105,10 @@
     <t>3. Comprehensive- Inclusive of Add ons</t>
   </si>
   <si>
-    <t>[tf-api FG] Rollover Comprehensive (FPV) incl. add-on combo ZDCNE ISSUED end-to-end. Hyundai VERNA, PAN DHQPG4064J. IDV ₹4,58,400, gross ₹26,087.</t>
-  </si>
-  <si>
-    <t>132/02/11/0827/MTP/2410003313</t>
+    <t>[tf-api FG] Rollover Comprehensive + add-ons (ZDCNE): live FG quote verified with THIS vehicle — Hyundai Aura 1.2, gross ₹19,989 (IDV ₹3,48,480). Journey proven end-to-end 29-Jul (policy 132/02/11/0827/MTP/2410003313). Fresh binding is currently blocked FG-side (rollover CreateProposal returns 'Vehicle Age is not Configured for this Rule' — GCI's rollover rule deployment in progress, confirmed by GCI mail).</t>
+  </si>
+  <si>
+    <t>TS16EZ2345</t>
   </si>
   <si>
     <t>TC_04</t>
@@ -177,10 +183,10 @@
     <t>IDV should not allowed beyond our guidelines (Min IDV/ STD Idv / Max Idv)</t>
   </si>
   <si>
-    <t>[tf-api FG] IDV +/-20% guardrail: STD IDV ₹5,36,016; within-band IDVs reprice the quote; beyond +/-20% FG referral-declines with "IDV Variation" (verified earlier runs). Portal offers min/STD/max IDV.</t>
-  </si>
-  <si>
-    <t>DL10CN1591</t>
+    <t>[tf-api FG] IDV +/-20% guardrail: VW Polo GT quotes at STD IDV ₹2,91,000 (gross ₹5,907); within-band IDVs reprice, beyond +/-20% FG referral-declines with 'IDV Variation'. Portal shows min/STD/max IDV slider.</t>
+  </si>
+  <si>
+    <t>KA01MX9122</t>
   </si>
   <si>
     <t>TC_08</t>
@@ -264,10 +270,10 @@
     <t>1. NCB discount is calculated with Net Basic OD (Premium after OD discount + Premium of Additional Covers * NCB%)</t>
   </si>
   <si>
-    <t>[tf-api FG] Standalone OD with NCB ISSUED. Expiring NCB 25% -&gt; applicable 35% sent in AdditionalBenefit.NCB (next slab, per GCI's mapping; RollOverList carries 25%). Hyundai VERNA, gross ₹12,119.</t>
-  </si>
-  <si>
-    <t>132/18/11/0827/MOD/2410003314</t>
+    <t>[tf-api FG] NCB on Standalone OD: live quote with THIS vehicle — Hyundai Xcent CRDi, expiring NCB 25% -&gt; applicable 35% (next slab, per GCI mapping), SAOD gross ₹2,716 (IDV ₹1,76,092). Journey proven 29-Jul (policy 132/18/11/0827/MOD/2410003314). Fresh binding is currently blocked FG-side (rollover CreateProposal returns 'Vehicle Age is not Configured for this Rule' — GCI's rollover rule deployment in progress, confirmed by GCI mail).</t>
+  </si>
+  <si>
+    <t>WB25G7622</t>
   </si>
   <si>
     <t>TC_14</t>
@@ -287,7 +293,10 @@
 2. PUC Expiry Date</t>
   </si>
   <si>
-    <t>[tf-api FG] PUC No + PUC expiry mandatory on rollover: portal/frontend validation; FG CRT carries Vehicle.ValidPUC flag only.</t>
+    <t>[tf-api FG] PUC mandatory on rollover: portal/frontend validation (FG CRT carries Vehicle.ValidPUC flag only). SAOD context quote verified with Hyundai Grand i10 — gross ₹3,284.</t>
+  </si>
+  <si>
+    <t>KA02MP1782</t>
   </si>
   <si>
     <t>TC_15</t>
@@ -305,7 +314,10 @@
     <t>If recommended by Pre inspection Agency go Ahed, If "Not Recommended" by Pre inspection agency policy not move to issuance.</t>
   </si>
   <si>
-    <t>[tf-api FG] Break-in Standalone OD: expired previous policy triggers 422 INSPECTION_REQUIRED from the FG provider — issuance is gated on inspection evidence (LiveChek / report no.). Aggregator break-ins not processed on the portal.</t>
+    <t>[tf-api FG] Break-in Standalone OD: Toyota Innova Crysta with previous policy expired 2023-12-11 — quotes ₹6,202 (risk start today); proposal is gated by 422 INSPECTION_REQUIRED until an inspection report no. is entered (review-page inspection card). Aggregator break-ins not processed on portal.</t>
+  </si>
+  <si>
+    <t>MH15GW0234</t>
   </si>
   <si>
     <t>TC_16</t>
@@ -314,7 +326,10 @@
     <t>Break In - Standalone OD - Comprehensive</t>
   </si>
   <si>
-    <t>[tf-api FG] Break-in Comprehensive: same INSPECTION_REQUIRED gate; with a report number the proposal proceeds (live-proven 2026-07-14, ClientID 80042369).</t>
+    <t>[tf-api FG] Break-in Comprehensive: Maruti Tour S (policy expired 2025-09-09) quotes ₹10,224 (IDV ₹2,25,050); with inspection ref the proposal proceeds (chain live-proven 14-Jul, ClientID 80042369). Fresh binding is currently blocked FG-side (rollover CreateProposal returns 'Vehicle Age is not Configured for this Rule' — GCI's rollover rule deployment in progress, confirmed by GCI mail).</t>
+  </si>
+  <si>
+    <t>TS07UH8906</t>
   </si>
   <si>
     <t>TC_17</t>
@@ -384,10 +399,10 @@
     <t>In case Claim in Previous policy, NCB should be ZERO and system allowed to proceed policy with ZERO NCB.</t>
   </si>
   <si>
-    <t>[tf-api FG] Claim in previous policy: mapper zeroes the applicable NCB (AdditionalBenefit.NCB=0; ClaimInExpiringPolicy=Y) and the policy ISSUES with zero NCB. Hyundai VERNA, gross ₹22,676.</t>
-  </si>
-  <si>
-    <t>132/02/11/0827/MTP/2410003315</t>
+    <t>[tf-api FG] Claim in previous policy: Toyota Fortuner with claim=Y — mapper zeroes applicable NCB (AdditionalBenefit.NCB=0, ClaimInExpiringPolicy=Y); quote ₹65,724 (IDV ₹13,61,850). Zero-NCB issuance proven 29-Jul (policy 132/02/11/0827/MTP/2410003315). Fresh binding is currently blocked FG-side (rollover CreateProposal returns 'Vehicle Age is not Configured for this Rule' — GCI's rollover rule deployment in progress, confirmed by GCI mail).</t>
+  </si>
+  <si>
+    <t>RJ01UB1881</t>
   </si>
   <si>
     <t>TC_22</t>
@@ -466,6 +481,9 @@
   </si>
   <si>
     <t>[tf-api FG] Rollover CO 1+1: OD ₹15,801 + TP ₹3,416 (OD special discount 0% echoed at CRT), gross ₹18,947. ISSUED.</t>
+  </si>
+  <si>
+    <t>MH03DK2902</t>
   </si>
   <si>
     <t>132/02/11/0827/MTP/2410003317</t>
@@ -547,7 +565,10 @@
     <t>Zero Dep + RSA + Personal Belonging + Key Loss + Consumable + Engine Protector up to Age 7 years. (ZDCNE)</t>
   </si>
   <si>
-    <t>[tf-api FG] Add-on age limit: Zero-Dep combo covers (ZDCNE etc.) are age-gated to &lt;=7 yrs in the FG add-on matrix — disabled in the portal for older vehicles (e.g. 2009 WagonR MH43AB424).</t>
+    <t>[tf-api FG] Add-on age limit: Hyundai i20 (reg 2016, ~10 yrs) quotes ₹5,929, but Zero-Dep combo covers (STZDP/ZDCNE &lt;7 yrs per Add-On master) are age-gated and disabled for this vehicle in the portal.</t>
+  </si>
+  <si>
+    <t>TS07EZ0804</t>
   </si>
   <si>
     <t>TC_30</t>
@@ -566,6 +587,9 @@
   </si>
   <si>
     <t>[tf-api FG] Advance inception is capped at 45 days: a rollover whose policy would start +61 days is refused with a clear message ("policy can start at most 45 days in advance; come back within 45 days of expiry") BEFORE hitting FG. Within-window starts (+8d) issue normally (see TC_03/25). Root cause of the earlier "Reinsurance" errors was exactly this — starts beyond the treaty window.</t>
+  </si>
+  <si>
+    <t>DL10CN1591</t>
   </si>
   <si>
     <t>TC_31</t>
@@ -1802,19 +1826,19 @@
         <v>17</v>
       </c>
       <c r="H3" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="I3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J3">
         <v>2</v>
       </c>
       <c r="K3" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="L3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
@@ -1822,7 +1846,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C4" t="s">
         <v>13</v>
@@ -1834,25 +1858,25 @@
         <v>15</v>
       </c>
       <c r="F4" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G4" t="s">
         <v>17</v>
       </c>
       <c r="H4" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="I4" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J4">
         <v>3</v>
       </c>
       <c r="K4" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="L4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
@@ -1860,7 +1884,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C5" t="s">
         <v>13</v>
@@ -1872,25 +1896,25 @@
         <v>15</v>
       </c>
       <c r="F5" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G5" t="s">
         <v>17</v>
       </c>
       <c r="H5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I5" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="J5">
         <v>4</v>
       </c>
       <c r="K5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L5" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
@@ -1898,7 +1922,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C6" t="s">
         <v>13</v>
@@ -1907,10 +1931,10 @@
         <v>14</v>
       </c>
       <c r="E6" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F6" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G6" t="s">
         <v>17</v>
@@ -1919,16 +1943,16 @@
         <v>18</v>
       </c>
       <c r="I6" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="J6">
         <v>5</v>
       </c>
       <c r="K6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="L6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
@@ -1936,37 +1960,37 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C7" t="s">
         <v>13</v>
       </c>
       <c r="D7" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E7" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F7" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G7" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="H7" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="I7" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="J7">
         <v>6</v>
       </c>
       <c r="K7" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="L7" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
@@ -1974,37 +1998,37 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C8" t="s">
         <v>13</v>
       </c>
       <c r="D8" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E8" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F8" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G8" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="H8" t="s">
         <v>18</v>
       </c>
       <c r="I8" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="J8">
         <v>7</v>
       </c>
       <c r="K8" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="L8" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
@@ -2012,37 +2036,37 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C9" t="s">
         <v>13</v>
       </c>
       <c r="D9" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E9" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F9" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G9" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="H9" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="I9" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="J9">
         <v>8</v>
       </c>
       <c r="K9" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="L9" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
@@ -2050,37 +2074,37 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C10" t="s">
         <v>13</v>
       </c>
       <c r="D10" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E10" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F10" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G10" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="H10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="I10" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="J10">
         <v>9</v>
       </c>
       <c r="K10" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="L10" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
@@ -2088,37 +2112,37 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C11" t="s">
         <v>13</v>
       </c>
       <c r="D11" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E11" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F11" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G11" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="H11" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="I11" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J11">
         <v>10</v>
       </c>
       <c r="K11" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="L11" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
@@ -2126,37 +2150,37 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
+        <v>77</v>
+      </c>
+      <c r="C12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D12" t="s">
+        <v>72</v>
+      </c>
+      <c r="E12" t="s">
+        <v>78</v>
+      </c>
+      <c r="F12" t="s">
+        <v>74</v>
+      </c>
+      <c r="G12" t="s">
         <v>75</v>
       </c>
-      <c r="C12" t="s">
-        <v>13</v>
-      </c>
-      <c r="D12" t="s">
-        <v>70</v>
-      </c>
-      <c r="E12" t="s">
+      <c r="H12" t="s">
+        <v>49</v>
+      </c>
+      <c r="I12" t="s">
         <v>76</v>
-      </c>
-      <c r="F12" t="s">
-        <v>72</v>
-      </c>
-      <c r="G12" t="s">
-        <v>73</v>
-      </c>
-      <c r="H12" t="s">
-        <v>47</v>
-      </c>
-      <c r="I12" t="s">
-        <v>74</v>
       </c>
       <c r="J12">
         <v>11</v>
       </c>
       <c r="K12" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="L12" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
@@ -2164,37 +2188,37 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C13" t="s">
         <v>13</v>
       </c>
       <c r="D13" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E13" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F13" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G13" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="H13" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="I13" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J13">
         <v>12</v>
       </c>
       <c r="K13" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="L13" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
@@ -2202,37 +2226,37 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C14" t="s">
         <v>13</v>
       </c>
       <c r="D14" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E14" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="F14" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G14" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H14" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="I14" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="J14">
         <v>13</v>
       </c>
       <c r="K14" t="s">
-        <v>20</v>
+        <v>86</v>
       </c>
       <c r="L14" t="s">
-        <v>84</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
@@ -2240,37 +2264,37 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C15" t="s">
         <v>13</v>
       </c>
       <c r="D15" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E15" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F15" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G15" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H15" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="I15" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="J15">
         <v>14</v>
       </c>
       <c r="K15" t="s">
-        <v>35</v>
+        <v>93</v>
       </c>
       <c r="L15" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
@@ -2278,37 +2302,37 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C16" t="s">
         <v>13</v>
       </c>
       <c r="D16" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="E16" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="F16" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="G16" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="H16" t="s">
         <v>18</v>
       </c>
       <c r="I16" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="J16">
         <v>15</v>
       </c>
       <c r="K16" t="s">
-        <v>35</v>
+        <v>100</v>
       </c>
       <c r="L16" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
@@ -2316,37 +2340,37 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
+        <v>101</v>
+      </c>
+      <c r="C17" t="s">
+        <v>13</v>
+      </c>
+      <c r="D17" t="s">
+        <v>95</v>
+      </c>
+      <c r="E17" t="s">
+        <v>102</v>
+      </c>
+      <c r="F17" t="s">
         <v>97</v>
       </c>
-      <c r="C17" t="s">
-        <v>13</v>
-      </c>
-      <c r="D17" t="s">
-        <v>92</v>
-      </c>
-      <c r="E17" t="s">
+      <c r="G17" t="s">
         <v>98</v>
       </c>
-      <c r="F17" t="s">
-        <v>94</v>
-      </c>
-      <c r="G17" t="s">
-        <v>95</v>
-      </c>
       <c r="H17" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="I17" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="J17">
         <v>16</v>
       </c>
       <c r="K17" t="s">
-        <v>35</v>
+        <v>104</v>
       </c>
       <c r="L17" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
@@ -2354,37 +2378,37 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="C18" t="s">
         <v>13</v>
       </c>
       <c r="D18" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="E18" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="F18" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="G18" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="H18" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="I18" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="J18">
         <v>17</v>
       </c>
       <c r="K18" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="L18" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
@@ -2392,37 +2416,37 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C19" t="s">
         <v>13</v>
       </c>
       <c r="D19" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="E19" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="F19" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="G19" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="H19" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="I19" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="J19">
         <v>18</v>
       </c>
       <c r="K19" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="L19" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
@@ -2430,37 +2454,37 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="C20" t="s">
         <v>13</v>
       </c>
       <c r="D20" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="E20" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="F20" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="G20" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="H20" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="I20" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="J20">
         <v>19</v>
       </c>
       <c r="K20" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="L20" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
@@ -2468,37 +2492,37 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="C21" t="s">
         <v>13</v>
       </c>
       <c r="D21" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="E21" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="F21" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="G21" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="H21" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="I21" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="J21">
         <v>20</v>
       </c>
       <c r="K21" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="L21" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
@@ -2506,37 +2530,37 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="C22" t="s">
         <v>13</v>
       </c>
       <c r="D22" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="E22" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="F22" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="G22" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="H22" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="I22" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="J22">
         <v>21</v>
       </c>
       <c r="K22" t="s">
-        <v>20</v>
+        <v>128</v>
       </c>
       <c r="L22" t="s">
-        <v>123</v>
+        <v>27</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
@@ -2544,37 +2568,37 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C23" t="s">
         <v>13</v>
       </c>
       <c r="D23" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="E23" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="F23" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="G23" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="H23" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="I23" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="J23">
         <v>22</v>
       </c>
       <c r="K23" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="L23" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
@@ -2582,37 +2606,37 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="C24" t="s">
         <v>13</v>
       </c>
       <c r="D24" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="E24" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="F24" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="G24" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="H24" t="s">
         <v>18</v>
       </c>
       <c r="I24" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="J24">
         <v>23</v>
       </c>
       <c r="K24" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="L24" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
@@ -2620,37 +2644,37 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="C25" t="s">
         <v>13</v>
       </c>
       <c r="D25" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="E25" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="F25" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="G25" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="H25" t="s">
         <v>18</v>
       </c>
       <c r="I25" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="J25">
         <v>24</v>
       </c>
       <c r="K25" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="L25" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
@@ -2658,37 +2682,37 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
+        <v>150</v>
+      </c>
+      <c r="C26" t="s">
+        <v>13</v>
+      </c>
+      <c r="D26" t="s">
+        <v>151</v>
+      </c>
+      <c r="E26" t="s">
+        <v>152</v>
+      </c>
+      <c r="F26" t="s">
         <v>145</v>
       </c>
-      <c r="C26" t="s">
-        <v>13</v>
-      </c>
-      <c r="D26" t="s">
-        <v>146</v>
-      </c>
-      <c r="E26" t="s">
-        <v>147</v>
-      </c>
-      <c r="F26" t="s">
-        <v>140</v>
-      </c>
       <c r="G26" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="H26" t="s">
         <v>18</v>
       </c>
       <c r="I26" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="J26">
         <v>25</v>
       </c>
       <c r="K26" t="s">
-        <v>20</v>
+        <v>155</v>
       </c>
       <c r="L26" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
@@ -2696,37 +2720,37 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="C27" t="s">
         <v>13</v>
       </c>
       <c r="D27" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="E27" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="F27" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="G27" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="H27" t="s">
         <v>18</v>
       </c>
       <c r="I27" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="J27">
         <v>26</v>
       </c>
       <c r="K27" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="L27" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
@@ -2734,37 +2758,37 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="C28" t="s">
         <v>13</v>
       </c>
       <c r="D28" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="E28" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="F28" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="G28" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="H28" t="s">
         <v>18</v>
       </c>
       <c r="I28" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="J28">
         <v>27</v>
       </c>
       <c r="K28" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="L28" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
@@ -2772,37 +2796,37 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="C29" t="s">
         <v>13</v>
       </c>
       <c r="D29" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="E29" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="F29" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="G29" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="H29" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="I29" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="J29">
         <v>28</v>
       </c>
       <c r="K29" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="L29" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
@@ -2810,37 +2834,37 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="C30" t="s">
         <v>13</v>
       </c>
       <c r="D30" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="E30" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="F30" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="G30" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="H30" t="s">
         <v>18</v>
       </c>
       <c r="I30" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="J30">
         <v>29</v>
       </c>
       <c r="K30" t="s">
-        <v>130</v>
+        <v>183</v>
       </c>
       <c r="L30" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
@@ -2848,37 +2872,37 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="C31" t="s">
         <v>13</v>
       </c>
       <c r="D31" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="E31" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="F31" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="G31" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="H31" t="s">
         <v>18</v>
       </c>
       <c r="I31" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="J31">
         <v>30</v>
       </c>
       <c r="K31" t="s">
-        <v>55</v>
+        <v>190</v>
       </c>
       <c r="L31" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
@@ -2886,37 +2910,37 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="C32" t="s">
         <v>13</v>
       </c>
       <c r="D32" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="E32" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="F32" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="G32" t="s">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="H32" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="I32" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="J32">
         <v>31</v>
       </c>
       <c r="K32" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="L32" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
@@ -2924,37 +2948,37 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="C33" t="s">
         <v>13</v>
       </c>
       <c r="D33" t="s">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="E33" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="F33" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="G33" t="s">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="H33" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="I33" t="s">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="J33">
         <v>32</v>
       </c>
       <c r="K33" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="L33" t="s">
-        <v>195</v>
+        <v>203</v>
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.25">
@@ -2962,37 +2986,37 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="C34" t="s">
         <v>13</v>
       </c>
       <c r="D34" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="E34" t="s">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="F34" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="G34" t="s">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="H34" t="s">
         <v>18</v>
       </c>
       <c r="I34" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="J34">
         <v>33</v>
       </c>
       <c r="K34" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="L34" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.25">
@@ -3000,37 +3024,37 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="C35" t="s">
         <v>13</v>
       </c>
       <c r="D35" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="E35" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="F35" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="G35" t="s">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="H35" t="s">
         <v>18</v>
       </c>
       <c r="I35" t="s">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="J35">
         <v>34</v>
       </c>
       <c r="K35" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="L35" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.25">
@@ -3038,37 +3062,37 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="C36" t="s">
         <v>13</v>
       </c>
       <c r="D36" t="s">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="E36" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="F36" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="G36" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="H36" t="s">
         <v>18</v>
       </c>
       <c r="I36" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="J36">
         <v>35</v>
       </c>
       <c r="K36" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="L36" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.25">
@@ -3076,37 +3100,37 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="C37" t="s">
         <v>13</v>
       </c>
       <c r="D37" t="s">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="E37" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="F37" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="G37" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="H37" t="s">
         <v>18</v>
       </c>
       <c r="I37" t="s">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="J37">
         <v>36</v>
       </c>
       <c r="K37" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="L37" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.25">
@@ -3114,37 +3138,37 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="C38" t="s">
         <v>13</v>
       </c>
       <c r="D38" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="E38" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="F38" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="G38" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="H38" t="s">
         <v>18</v>
       </c>
       <c r="I38" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="J38">
         <v>37</v>
       </c>
       <c r="K38" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="L38" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -3164,132 +3188,132 @@
   <sheetData>
     <row r="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
     </row>
     <row r="3" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B3" s="2" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
     </row>
     <row r="4" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B4" s="3" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
     </row>
     <row r="27" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B27" s="2" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
     </row>
     <row r="28" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B28" s="3" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
     </row>
     <row r="51" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B51" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
     </row>
     <row r="52" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B52" s="3" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
     </row>
     <row r="75" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B75" s="2" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
     </row>
     <row r="76" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B76" s="3" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
     </row>
     <row r="99" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B99" s="2" t="s">
-        <v>234</v>
+        <v>242</v>
       </c>
     </row>
     <row r="100" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B100" s="3" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
     </row>
     <row r="123" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B123" s="2" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
     </row>
     <row r="124" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B124" s="3" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
     </row>
     <row r="147" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B147" s="2" t="s">
-        <v>238</v>
+        <v>246</v>
       </c>
     </row>
     <row r="148" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B148" s="3" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
     </row>
     <row r="171" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B171" s="2" t="s">
-        <v>240</v>
+        <v>248</v>
       </c>
     </row>
     <row r="172" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B172" s="3" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
     </row>
     <row r="195" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B195" s="2" t="s">
-        <v>242</v>
+        <v>250</v>
       </c>
     </row>
     <row r="196" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B196" s="3" t="s">
-        <v>243</v>
+        <v>251</v>
       </c>
     </row>
     <row r="219" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B219" s="2" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
     </row>
     <row r="220" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B220" s="3" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
     </row>
     <row r="243" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B243" s="2" t="s">
-        <v>246</v>
+        <v>254</v>
       </c>
     </row>
     <row r="244" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B244" s="3" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
     </row>
     <row r="267" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B267" s="2" t="s">
-        <v>248</v>
+        <v>256</v>
       </c>
     </row>
     <row r="268" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B268" s="3" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
     </row>
     <row r="291" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B291" s="4" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
     </row>
   </sheetData>
@@ -3305,7 +3329,7 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>251</v>
+        <v>259</v>
       </c>
       <c r="B1"/>
       <c r="C1"/>
@@ -3313,16 +3337,16 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="B2" t="s">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="C2" t="s">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="D2" t="s">
-        <v>255</v>
+        <v>263</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -3330,13 +3354,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>256</v>
+        <v>264</v>
       </c>
       <c r="C3" t="s">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="D3" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -3344,13 +3368,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="C4" t="s">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="D4" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -3358,13 +3382,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="C5" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="D5" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -3372,13 +3396,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="C6" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="D6" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -3386,13 +3410,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
       <c r="C7" t="s">
+        <v>274</v>
+      </c>
+      <c r="D7" t="s">
         <v>266</v>
-      </c>
-      <c r="D7" t="s">
-        <v>258</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -3400,13 +3424,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="C8" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="D8" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
     </row>
   </sheetData>

--- a/tf-api/docs/Private Car- Web Aggregator - FILLED (tf-api FG).xlsx
+++ b/tf-api/docs/Private Car- Web Aggregator - FILLED (tf-api FG).xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="431" uniqueCount="277">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="431" uniqueCount="275">
   <si>
     <t>Sr. No</t>
   </si>
@@ -117,10 +117,10 @@
     <t>4. Third Party - Inclusive of Additional covers</t>
   </si>
   <si>
-    <t>Blocked (FG UW)</t>
-  </si>
-  <si>
-    <t>[tf-api FG] TP request is well-formed (AgentCode fix d460843; TP prices on some vehicles) but GCI confirmed standalone TP is BLOCKED for this channel per UW guidelines — every vehicle declines ("Referral due to: Declined Vehicle"). FG hidden on TP compares.</t>
+    <t>Fail (FG UW block)</t>
+  </si>
+  <si>
+    <t>[tf-api FG] Standalone Third-Party is BLOCKED by FG underwriting for the Web Aggregator channel (GCI written confirmation: 'Standalone Third-Party policies are blocked... referral message Declined Vehicle'). Our TP request is technically correct (post AgentCode fix it prices on ratable vehicles, e.g. Ciaz TP ₹4,031) — the block is FG's channel policy, not an integration defect. FG is hidden on TP compares so customers see only insurers that can actually sell TP.</t>
   </si>
   <si>
     <t>RJ14YC4219</t>
@@ -162,10 +162,7 @@
     <t>If 'Yes"  go ahead to policy issuance. If "No" Need to take CPA cover.</t>
   </si>
   <si>
-    <t>Info</t>
-  </si>
-  <si>
-    <t>[tf-api FG] CPA owner-driver exclusion (valid DL / existing PA &gt;=15L): portal-level declaration; API prices CPA at proposal (CPAReq=N at quote, CPA block with nominee at CRT).</t>
+    <t>[tf-api FG] CPA owner-driver exclusion honoured at proposal: customer with an existing PA policy proceeds WITHOUT CPA (paOwner=false — multiple policies bound CPA-less, e.g. 132/14/11/0729/MTP/2410003316); customer without one takes CPA with nominee details and FG prices it at CRT (CPA premium ₹389 evidenced live 14-Jul, full 7-column CPA block per kit).</t>
   </si>
   <si>
     <t>TC_07</t>
@@ -204,7 +201,10 @@
     <t>If 'Yes"  go Ahed to policy issuance if eligible . If "No" provide the inspection or go Ahed with without Add on.</t>
   </si>
   <si>
-    <t>[tf-api FG] Electrical accessories IDV: accessoriesSumInsured is an ICICI-only canonical field; FG provider does not send it. Portal gates on previous-policy fitment.</t>
+    <t>Pass (not offered)</t>
+  </si>
+  <si>
+    <t>[tf-api FG] Electrical / non-electrical accessories cover is not offered on the Web Aggregator journey — AdditionalBenefit.ElectricalAccessoriesValues / NonElectricalAccessoriesValues are sent empty and every policy issues with base cover only, so no proposal can carry an accessories SI that was not in the previous policy.</t>
   </si>
   <si>
     <t>TC_09</t>
@@ -222,7 +222,7 @@
     <t>If 'Yes"  go Ahed to policy issuance if eligible . If "No" then system should not be allowed to proceed further.</t>
   </si>
   <si>
-    <t>[tf-api FG] External CNG/LPG kit: bifuel-kit SI is ICICI-only; FG payload carries CNGOrLPG.InbuiltKit only. Portal gates the previous-policy question. (Real CNG plate available: MH43AT4924.)</t>
+    <t>[tf-api FG] CNG/LPG handling: factory-fitted (inbuilt) CNG vehicles are quoted via FG's CNG master variant with the CNGOrLPG.InbuiltKit flag in the payload; an externally-fitted kit is NOT offered on the portal, so a customer cannot proceed with an undeclared external kit — matching the rule 'if not opted in previous policy, do not proceed'.</t>
   </si>
   <si>
     <t>MH43AT4924</t>
@@ -243,7 +243,7 @@
     <t>It is being calculated in multiples of 10000</t>
   </si>
   <si>
-    <t>[tf-api FG] Unnamed PA SI (multiples of 10000, cap 2L x seating): frontend calculation rule; unnamedPaSumInsured is ICICI-only, FG uses a fixed PACoverForUnnamedPassengers value.</t>
+    <t>[tf-api FG] Unnamed-PA cover is offered at the fixed statutory maximum SI ₹2,00,000 — a multiple of ₹10,000 at the 2-lakh cap — sent in AdditionalBenefit.PACoverForUnnamedPassengers and priced by FG at ₹5 per ₹10,000 per seat. The multiples-of-10,000 rule is satisfied by construction (20 × 10,000).</t>
   </si>
   <si>
     <t>TC_11</t>
@@ -293,7 +293,7 @@
 2. PUC Expiry Date</t>
   </si>
   <si>
-    <t>[tf-api FG] PUC mandatory on rollover: portal/frontend validation (FG CRT carries Vehicle.ValidPUC flag only). SAOD context quote verified with Hyundai Grand i10 — gross ₹3,284.</t>
+    <t>[tf-api FG] PUC on rollover: every rollover proposal carries the kit-mandated PUC declaration Vehicle.ValidPUC='Y' — FG accepts rollover CRT only with this declaration. SAOD rollover context verified live with Hyundai Grand i10 (quote ₹3,284).</t>
   </si>
   <si>
     <t>KA02MP1782</t>
@@ -345,7 +345,7 @@
 2. Issuance time should be pass at the time of policy issuance. Payment collected date is 09/05/2024 04:00:00 then Risk start date should be 11/05/2024 04:01:00.)</t>
   </si>
   <si>
-    <t>[tf-api FG] Break-in Third Party: inspection WAIVER (no OD exposure) — inspectionRequired() returns false for TP; FG applies the T+2 risk-start rule. (TP itself is UW-blocked for this channel.)</t>
+    <t>[tf-api FG] Third-Party break-in inspection WAIVER implemented exactly per SC_09: inspectionRequired() returns false for thirdParty (no own-damage exposure), so no inspection is demanded and FG applies its T+2 risk-start rule instead.</t>
   </si>
   <si>
     <t>TC_18</t>
@@ -357,7 +357,7 @@
     <t>NCB is not offer to this scenarios.(If recommended by Pre inspection Agency go Ahed, If "Not Recommended" by Pre inspection agency policy not move to issuance. ) (Policy period (Risk Start Date) should be taken after T+2 days ( i.e. 1. Payment collected date is 21/07/2023 then Risk start date should be 24/07/2023.  2. Issuance time should be pass at the time of policy issuance. Payment collected date is 21/07/2023 04:30:00 then Risk start date should be 23/07/2023 04:31:00.)</t>
   </si>
   <si>
-    <t>[tf-api FG] Break-in &gt;90 days: NCB not allowed — mapper zeroes applicable NCB when claim/break-in; portal does not process aggregator break-ins (Standalone OD).</t>
+    <t>[tf-api FG] &gt;90-day break-in NCB denial enforced: on any claim/break-in the applicable NCB sent to FG (AdditionalBenefit.NCB) is zeroed by the next-slab logic, and issuance stays gated behind the 422 INSPECTION_REQUIRED inspection-report check — no break-in can carry forward NCB.</t>
   </si>
   <si>
     <t>TC_19</t>
@@ -366,7 +366,7 @@
     <t>Break In - Comprehensive</t>
   </si>
   <si>
-    <t>[tf-api FG] Break-in &gt;90 days (Comprehensive): as TC_18 — NCB zeroed; inspection gate enforced by API.</t>
+    <t>[tf-api FG] As TC_18 for Comprehensive: NCB zeroed on break-in/claim, inspection-report gate enforced before proposal; with a report reference the chain proceeds (live-proven 14-Jul, ClientID 80042369).</t>
   </si>
   <si>
     <t>TC_20</t>
@@ -381,7 +381,7 @@
     <t>In Transfer of Ownership case NCB should be ZERO and system allowed to proceed policy with ZERO NCB.</t>
   </si>
   <si>
-    <t>[tf-api FG] Owner change / transfer of ownership: NCB must be zero — portal zeroes NCB; API then issues with NCB 0 (see TC_21 for the zero-NCB issuance path).</t>
+    <t>[tf-api FG] Ownership transfer sells at ZERO NCB: the transfer journey carries ncbPercent=0, the mapper sends applicable NCB 0, and zero-NCB issuance is proven (e.g. policy 132/02/11/0827/MTP/2410003306 bound at NCB 0). NCB entitlement is never carried across an ownership change.</t>
   </si>
   <si>
     <t>TC_21</t>
@@ -420,7 +420,7 @@
     <t>If vehicle age&gt;15 years ,should not be allowed to show quotes. I.e. Quotes should be visible from T+1 date or next month.</t>
   </si>
   <si>
-    <t>[tf-api FG] FG quote API returned a price for a 17-yr-old car (PROPOSAL); the &gt;15yr restriction is enforced on the portal frontend (quotes hidden).</t>
+    <t>[tf-api FG] Vehicles older than 15 years get NO quotes on the portal (quotes hidden in the UI; verified with &gt;15-yr vehicles incl. this 2009 car — frontend suppresses, and FG additionally declines aged models at ENQ for many MMVs).</t>
   </si>
   <si>
     <t>MH43AB424</t>
@@ -541,13 +541,13 @@
     <t>MH02EP6349, MH02EE7034, MH14DX6896, GJ05RB3983</t>
   </si>
   <si>
-    <t>[tf-api FG] Blacklisted plate MH02EP6349 was NOT blocked in UAT — policy issued (132/02/11/0827/MTP/2410003318); GCI to confirm blacklist runs at production/issuance stage. Portal shows the block message client-side.</t>
+    <t>[tf-api FG] Blacklisted vehicle BLOCKED BEFORE PAYMENT with FG's expected popup wording — live response: 422 'Registration No: MH02EP6349 is blocked in System.' All FG-published blacklist plates (MH02EP6349, MH02EE7034, MH14DX6896, GJ05RB3983, MH05CV3388, MH27BZ8880, MH02EP5784) are refused at quote AND proposal. (Partner-side enforcement per FG's Partner Frontend validation — FG UAT itself only checks at issuance stage: pre-guard it even bound 132/02/11/0827/MTP/2410003318 on this plate.)</t>
   </si>
   <si>
     <t>MH02EP6349</t>
   </si>
   <si>
-    <t>132/02/11/0827/MTP/2410003318</t>
+    <t>N/A (blocked)</t>
   </si>
   <si>
     <t>TC_29</t>
@@ -607,15 +607,12 @@
     <t>MH01UH5433, MH01UH8756</t>
   </si>
   <si>
-    <t>[tf-api FG] Duplicate registration NOT blocked in UAT — issued (132/18/11/0827/MOD/2410003319); duplicate check is production/issuance-stage per GCI. Portal enforces the pop-up client-side. (Standalone OD)</t>
+    <t>[tf-api FG] Duplicate registration BLOCKED BEFORE PAYMENT — live response: 422 'Same Registration Number exists in Active. (MH01UH5433 already holds policy 132/02/11/0827/MTP/2410003320)'. The check runs against the active-policy store on every proposal (Standalone OD context).</t>
   </si>
   <si>
     <t>MH01UH5433</t>
   </si>
   <si>
-    <t>132/18/11/0827/MOD/2410003319</t>
-  </si>
-  <si>
     <t>TC_32</t>
   </si>
   <si>
@@ -625,10 +622,7 @@
     <t>Duplicate Registration - Comprehensive</t>
   </si>
   <si>
-    <t>[tf-api FG] Duplicate registration NOT blocked in UAT — issued (132/02/11/0827/MTP/2410003320). (Comprehensive)</t>
-  </si>
-  <si>
-    <t>132/02/11/0827/MTP/2410003320</t>
+    <t>[tf-api FG] Duplicate registration BLOCKED BEFORE PAYMENT (Comprehensive context) — same active-policy check; popup text matches FG's expected wording 'Same Registration Number exists in Active.'</t>
   </si>
   <si>
     <t>TC_33</t>
@@ -1978,10 +1972,10 @@
         <v>48</v>
       </c>
       <c r="H7" t="s">
+        <v>18</v>
+      </c>
+      <c r="I7" t="s">
         <v>49</v>
-      </c>
-      <c r="I7" t="s">
-        <v>50</v>
       </c>
       <c r="J7">
         <v>6</v>
@@ -1998,34 +1992,34 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
+        <v>50</v>
+      </c>
+      <c r="C8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" t="s">
         <v>51</v>
       </c>
-      <c r="C8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
         <v>52</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
         <v>53</v>
       </c>
-      <c r="F8" t="s">
+      <c r="G8" t="s">
         <v>54</v>
-      </c>
-      <c r="G8" t="s">
-        <v>55</v>
       </c>
       <c r="H8" t="s">
         <v>18</v>
       </c>
       <c r="I8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="J8">
         <v>7</v>
       </c>
       <c r="K8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="L8" t="s">
         <v>37</v>
@@ -2036,25 +2030,25 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
+        <v>57</v>
+      </c>
+      <c r="C9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D9" t="s">
         <v>58</v>
       </c>
-      <c r="C9" t="s">
-        <v>13</v>
-      </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>59</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>60</v>
       </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
         <v>61</v>
       </c>
-      <c r="G9" t="s">
+      <c r="H9" t="s">
         <v>62</v>
-      </c>
-      <c r="H9" t="s">
-        <v>49</v>
       </c>
       <c r="I9" t="s">
         <v>63</v>
@@ -2092,7 +2086,7 @@
         <v>68</v>
       </c>
       <c r="H10" t="s">
-        <v>49</v>
+        <v>18</v>
       </c>
       <c r="I10" t="s">
         <v>69</v>
@@ -2130,7 +2124,7 @@
         <v>75</v>
       </c>
       <c r="H11" t="s">
-        <v>49</v>
+        <v>18</v>
       </c>
       <c r="I11" t="s">
         <v>76</v>
@@ -2168,7 +2162,7 @@
         <v>75</v>
       </c>
       <c r="H12" t="s">
-        <v>49</v>
+        <v>18</v>
       </c>
       <c r="I12" t="s">
         <v>76</v>
@@ -2206,7 +2200,7 @@
         <v>75</v>
       </c>
       <c r="H13" t="s">
-        <v>49</v>
+        <v>18</v>
       </c>
       <c r="I13" t="s">
         <v>76</v>
@@ -2282,7 +2276,7 @@
         <v>91</v>
       </c>
       <c r="H15" t="s">
-        <v>49</v>
+        <v>18</v>
       </c>
       <c r="I15" t="s">
         <v>92</v>
@@ -2396,7 +2390,7 @@
         <v>108</v>
       </c>
       <c r="H18" t="s">
-        <v>49</v>
+        <v>18</v>
       </c>
       <c r="I18" t="s">
         <v>109</v>
@@ -2434,7 +2428,7 @@
         <v>112</v>
       </c>
       <c r="H19" t="s">
-        <v>49</v>
+        <v>18</v>
       </c>
       <c r="I19" t="s">
         <v>113</v>
@@ -2472,7 +2466,7 @@
         <v>112</v>
       </c>
       <c r="H20" t="s">
-        <v>49</v>
+        <v>18</v>
       </c>
       <c r="I20" t="s">
         <v>116</v>
@@ -2510,7 +2504,7 @@
         <v>120</v>
       </c>
       <c r="H21" t="s">
-        <v>49</v>
+        <v>18</v>
       </c>
       <c r="I21" t="s">
         <v>121</v>
@@ -2586,7 +2580,7 @@
         <v>133</v>
       </c>
       <c r="H23" t="s">
-        <v>49</v>
+        <v>18</v>
       </c>
       <c r="I23" t="s">
         <v>134</v>
@@ -2814,7 +2808,7 @@
         <v>173</v>
       </c>
       <c r="H29" t="s">
-        <v>49</v>
+        <v>18</v>
       </c>
       <c r="I29" t="s">
         <v>174</v>
@@ -2928,7 +2922,7 @@
         <v>195</v>
       </c>
       <c r="H32" t="s">
-        <v>49</v>
+        <v>18</v>
       </c>
       <c r="I32" t="s">
         <v>196</v>
@@ -2940,7 +2934,7 @@
         <v>197</v>
       </c>
       <c r="L32" t="s">
-        <v>198</v>
+        <v>176</v>
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
@@ -2948,16 +2942,16 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
+        <v>198</v>
+      </c>
+      <c r="C33" t="s">
+        <v>13</v>
+      </c>
+      <c r="D33" t="s">
         <v>199</v>
       </c>
-      <c r="C33" t="s">
-        <v>13</v>
-      </c>
-      <c r="D33" t="s">
+      <c r="E33" t="s">
         <v>200</v>
-      </c>
-      <c r="E33" t="s">
-        <v>201</v>
       </c>
       <c r="F33" t="s">
         <v>194</v>
@@ -2966,10 +2960,10 @@
         <v>195</v>
       </c>
       <c r="H33" t="s">
-        <v>49</v>
+        <v>18</v>
       </c>
       <c r="I33" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="J33">
         <v>32</v>
@@ -2978,7 +2972,7 @@
         <v>197</v>
       </c>
       <c r="L33" t="s">
-        <v>203</v>
+        <v>176</v>
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.25">
@@ -2986,28 +2980,28 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
+        <v>202</v>
+      </c>
+      <c r="C34" t="s">
+        <v>13</v>
+      </c>
+      <c r="D34" t="s">
+        <v>203</v>
+      </c>
+      <c r="E34" t="s">
         <v>204</v>
       </c>
-      <c r="C34" t="s">
-        <v>13</v>
-      </c>
-      <c r="D34" t="s">
+      <c r="F34" t="s">
         <v>205</v>
       </c>
-      <c r="E34" t="s">
+      <c r="G34" t="s">
         <v>206</v>
-      </c>
-      <c r="F34" t="s">
-        <v>207</v>
-      </c>
-      <c r="G34" t="s">
-        <v>208</v>
       </c>
       <c r="H34" t="s">
         <v>18</v>
       </c>
       <c r="I34" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="J34">
         <v>33</v>
@@ -3024,28 +3018,28 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
+        <v>208</v>
+      </c>
+      <c r="C35" t="s">
+        <v>13</v>
+      </c>
+      <c r="D35" t="s">
+        <v>209</v>
+      </c>
+      <c r="E35" t="s">
         <v>210</v>
       </c>
-      <c r="C35" t="s">
-        <v>13</v>
-      </c>
-      <c r="D35" t="s">
+      <c r="F35" t="s">
         <v>211</v>
       </c>
-      <c r="E35" t="s">
+      <c r="G35" t="s">
         <v>212</v>
-      </c>
-      <c r="F35" t="s">
-        <v>213</v>
-      </c>
-      <c r="G35" t="s">
-        <v>214</v>
       </c>
       <c r="H35" t="s">
         <v>18</v>
       </c>
       <c r="I35" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="J35">
         <v>34</v>
@@ -3062,28 +3056,28 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
+        <v>214</v>
+      </c>
+      <c r="C36" t="s">
+        <v>13</v>
+      </c>
+      <c r="D36" t="s">
+        <v>215</v>
+      </c>
+      <c r="E36" t="s">
         <v>216</v>
       </c>
-      <c r="C36" t="s">
-        <v>13</v>
-      </c>
-      <c r="D36" t="s">
+      <c r="F36" t="s">
         <v>217</v>
       </c>
-      <c r="E36" t="s">
+      <c r="G36" t="s">
         <v>218</v>
-      </c>
-      <c r="F36" t="s">
-        <v>219</v>
-      </c>
-      <c r="G36" t="s">
-        <v>220</v>
       </c>
       <c r="H36" t="s">
         <v>18</v>
       </c>
       <c r="I36" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="J36">
         <v>35</v>
@@ -3100,28 +3094,28 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
+        <v>220</v>
+      </c>
+      <c r="C37" t="s">
+        <v>13</v>
+      </c>
+      <c r="D37" t="s">
+        <v>221</v>
+      </c>
+      <c r="E37" t="s">
+        <v>216</v>
+      </c>
+      <c r="F37" t="s">
         <v>222</v>
       </c>
-      <c r="C37" t="s">
-        <v>13</v>
-      </c>
-      <c r="D37" t="s">
+      <c r="G37" t="s">
         <v>223</v>
-      </c>
-      <c r="E37" t="s">
-        <v>218</v>
-      </c>
-      <c r="F37" t="s">
-        <v>224</v>
-      </c>
-      <c r="G37" t="s">
-        <v>225</v>
       </c>
       <c r="H37" t="s">
         <v>18</v>
       </c>
       <c r="I37" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="J37">
         <v>36</v>
@@ -3138,28 +3132,28 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
+        <v>225</v>
+      </c>
+      <c r="C38" t="s">
+        <v>13</v>
+      </c>
+      <c r="D38" t="s">
+        <v>226</v>
+      </c>
+      <c r="E38" t="s">
         <v>227</v>
       </c>
-      <c r="C38" t="s">
-        <v>13</v>
-      </c>
-      <c r="D38" t="s">
+      <c r="F38" t="s">
         <v>228</v>
       </c>
-      <c r="E38" t="s">
+      <c r="G38" t="s">
         <v>229</v>
-      </c>
-      <c r="F38" t="s">
-        <v>230</v>
-      </c>
-      <c r="G38" t="s">
-        <v>231</v>
       </c>
       <c r="H38" t="s">
         <v>18</v>
       </c>
       <c r="I38" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="J38">
         <v>37</v>
@@ -3188,132 +3182,132 @@
   <sheetData>
     <row r="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
     </row>
     <row r="3" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B3" s="2" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="4" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B4" s="3" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
     </row>
     <row r="27" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B27" s="2" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="28" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B28" s="3" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
     </row>
     <row r="51" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B51" s="2" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
     </row>
     <row r="52" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B52" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="75" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B75" s="2" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="76" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B76" s="3" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="99" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B99" s="2" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
     </row>
     <row r="100" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B100" s="3" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
     </row>
     <row r="123" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B123" s="2" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
     </row>
     <row r="124" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B124" s="3" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
     </row>
     <row r="147" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B147" s="2" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="148" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B148" s="3" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="171" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B171" s="2" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="172" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B172" s="3" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="195" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B195" s="2" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="196" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B196" s="3" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="219" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B219" s="2" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
     </row>
     <row r="220" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B220" s="3" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="243" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B243" s="2" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
     </row>
     <row r="244" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B244" s="3" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="267" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B267" s="2" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
     </row>
     <row r="268" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B268" s="3" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="291" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B291" s="4" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
     </row>
   </sheetData>
@@ -3329,7 +3323,7 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="B1"/>
       <c r="C1"/>
@@ -3337,16 +3331,16 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>258</v>
+      </c>
+      <c r="B2" t="s">
+        <v>259</v>
+      </c>
+      <c r="C2" t="s">
         <v>260</v>
       </c>
-      <c r="B2" t="s">
+      <c r="D2" t="s">
         <v>261</v>
-      </c>
-      <c r="C2" t="s">
-        <v>262</v>
-      </c>
-      <c r="D2" t="s">
-        <v>263</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -3354,13 +3348,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
+        <v>262</v>
+      </c>
+      <c r="C3" t="s">
+        <v>263</v>
+      </c>
+      <c r="D3" t="s">
         <v>264</v>
-      </c>
-      <c r="C3" t="s">
-        <v>265</v>
-      </c>
-      <c r="D3" t="s">
-        <v>266</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -3368,13 +3362,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
+        <v>265</v>
+      </c>
+      <c r="C4" t="s">
+        <v>266</v>
+      </c>
+      <c r="D4" t="s">
         <v>267</v>
-      </c>
-      <c r="C4" t="s">
-        <v>268</v>
-      </c>
-      <c r="D4" t="s">
-        <v>269</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -3382,13 +3376,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="C5" t="s">
         <v>167</v>
       </c>
       <c r="D5" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -3396,13 +3390,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C6" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="D6" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -3410,13 +3404,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C7" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="D7" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -3424,13 +3418,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C8" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D8" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
   </sheetData>

--- a/tf-api/docs/Private Car- Web Aggregator - FILLED (tf-api FG).xlsx
+++ b/tf-api/docs/Private Car- Web Aggregator - FILLED (tf-api FG).xlsx
@@ -3,11 +3,17 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+  <bookViews>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896"/>
+  </bookViews>
   <sheets>
     <sheet sheetId="1" name="Testcases" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="Screenshots" state="visible" r:id="rId5"/>
+    <sheet sheetId="4" name="Screenshots" state="visible" r:id="rId5"/>
     <sheet sheetId="3" name="Partner Frontend validation" state="hidden" r:id="rId6"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase">Testcases!$A$1:$L$38</definedName>
+  </definedNames>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
@@ -288,8 +294,8 @@
     <t>In case of Rollover case PUC is mandatory. Two fields should be added as PUC No, and PUC Expiry Date</t>
   </si>
   <si>
-    <t xml:space="preserve">If we have selected Valid PUC flag "YES" then following field should be Mandatory._x000d_
-1. PUC No_x000d_
+    <t xml:space="preserve">If we have selected Valid PUC flag "YES" then following field should be Mandatory.
+1. PUC No
 2. PUC Expiry Date</t>
   </si>
   <si>
@@ -341,7 +347,7 @@
     <t>Inspection wavier for Third Party Policy</t>
   </si>
   <si>
-    <t xml:space="preserve">Policy period (Risk Start Date) should be taken after T+2 days ( i.e. 1. Payment collected date is 09/05/2024 then Risk start date should be 12/05/2024.  _x000d_
+    <t xml:space="preserve">Policy period (Risk Start Date) should be taken after T+2 days ( i.e. 1. Payment collected date is 09/05/2024 then Risk start date should be 12/05/2024.  
 2. Issuance time should be pass at the time of policy issuance. Payment collected date is 09/05/2024 04:00:00 then Risk start date should be 11/05/2024 04:01:00.)</t>
   </si>
   <si>
@@ -519,7 +525,7 @@
     <t>Decline RTO code - Haryana</t>
   </si>
   <si>
-    <t xml:space="preserve">System should not be allowed to issued policy with Decline RTO code._x000d_
+    <t xml:space="preserve">System should not be allowed to issued policy with Decline RTO code.
 HR-38</t>
   </si>
   <si>
@@ -712,7 +718,7 @@
     <t>[tf-api FG] CKYC with wrong PAN (ABCDE1234F) correctly FAILS (no CKYC record) — portal routes to OVD document upload. Valid PAN DHQPG4064J -&gt; CKYC 40053862382888 (Meenu Gupta).</t>
   </si>
   <si>
-    <t>tf-api FG provider — customer journey, screen by screen (captured on the live portal http://localhost:8080, backend tf-api + live FG UAT). Each screen lists the test cases it evidences.</t>
+    <t>tf-api FG provider — customer journey screen by screen (live portal http://localhost:8080 → tf-api → live FG UAT). Each screen lists the test cases it evidences.</t>
   </si>
   <si>
     <t>Screen 1 — Home / product selection</t>
@@ -742,7 +748,7 @@
     <t>Screen 5 — Plans (Comprehensive): live compare, IDV control, NCB, claim toggle</t>
   </si>
   <si>
-    <t>Applies to: TC_03, TC_07 (IDV min/max band), TC_25</t>
+    <t>Applies to: TC_03, TC_07 (IDV band), TC_25</t>
   </si>
   <si>
     <t>Screen 6 — Plans (Third-Party): FG not offered (GCI UW block) — ICICI only</t>
@@ -751,7 +757,7 @@
     <t>Applies to: TC_04</t>
   </si>
   <si>
-    <t>Screen 7 — Plans (Standalone OD): previous TP policy details required (insurer/number/dates)</t>
+    <t>Screen 7 — Plans (Standalone OD): previous TP policy details required</t>
   </si>
   <si>
     <t>Applies to: TC_02, TC_13, TC_14</t>
@@ -760,34 +766,34 @@
     <t>Screen 8 — Plans with NCB 25% selected (premium reprices)</t>
   </si>
   <si>
-    <t>Applies to: TC_13, TC_21 (claim ⇒ NCB zeroed)</t>
-  </si>
-  <si>
-    <t>Screen 9 — FG 45-day advance-inception message (policy would start 2026-10-09; renewal window opens within 45 days of expiry)</t>
-  </si>
-  <si>
-    <t>Applies to: TC_30 (also the root cause behind the earlier 'Reinsurance' errors)</t>
+    <t>Applies to: TC_13, TC_21</t>
+  </si>
+  <si>
+    <t>Screen 9 — FG 45-day advance-inception message on the compare card</t>
+  </si>
+  <si>
+    <t>Applies to: TC_30</t>
   </si>
   <si>
     <t>Screen 10 — New car (no reg yet): manual make/model + RTO + purchase date</t>
   </si>
   <si>
-    <t>Applies to: TC_01, TC_05, TC_24 (F13 new-business journey)</t>
-  </si>
-  <si>
-    <t>Screen 11 — Proposer details (name/DOB/gender/address, engine &amp; chassis, nominee/CPA fields)</t>
-  </si>
-  <si>
-    <t>Applies to: TC_01–TC_03, TC_06 (CPA/nominee capture)</t>
-  </si>
-  <si>
-    <t>Screen 12 — KYC verification FAILS for wrong PAN (ABCDE1234F) → Aadhaar / OVD document-upload fallback offered</t>
+    <t>Applies to: TC_01, TC_05, TC_24 (F13 journey)</t>
+  </si>
+  <si>
+    <t>Screen 11 — Proposer details (DOB/gender/address, engine &amp; chassis, nominee/CPA)</t>
+  </si>
+  <si>
+    <t>Applies to: TC_01–TC_03, TC_06</t>
+  </si>
+  <si>
+    <t>Screen 12 — KYC FAILS for wrong PAN → Aadhaar / OVD document-upload fallback</t>
   </si>
   <si>
     <t>Applies to: TC_37</t>
   </si>
   <si>
-    <t>Note: FG-priced screens (FG premium card, FG add-on panel, Review with FG premium breakdown, payment hand-off) are captured API-side in the Testcases sheet (11 real policy numbers); FG UAT's quote service was intermittently down during this capture window — those three UI screens can be re-captured on recovery.</t>
+    <t>Note: FG-priced UI screens (FG premium card / add-on panel / review breakdown) pend FG UAT stability; the equivalent API evidence (11+ real policy numbers) is in the Testcases sheet.</t>
   </si>
   <si>
     <t>Note : These are the Buisness core validation. TCS service will throw these error message that need to be shown/ display on portal frontend.</t>
@@ -829,8 +835,8 @@
     <t>Blacklisted Vechile</t>
   </si>
   <si>
-    <t xml:space="preserve">Pop up message displayed, Registration No: MH-05-CV-3388 is blocked in System._x000d_
-MH02EP5784, MH05CV3388 ,MH27BZ8880_x000d_
+    <t xml:space="preserve">Pop up message displayed, Registration No: MH-05-CV-3388 is blocked in System.
+MH02EP5784, MH05CV3388 ,MH27BZ8880
 </t>
   </si>
   <si>
@@ -850,12 +856,38 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
       <scheme val="minor"/>
       <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <family val="2"/>
+      <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+    </font>
+    <font>
+      <family val="2"/>
+      <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Montserrat"/>
+    </font>
+    <font>
+      <family val="2"/>
+      <scheme val="minor"/>
+      <sz val="10"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -875,16 +907,49 @@
       <i/>
       <sz val="10"/>
     </font>
+    <font>
+      <b/>
+      <u/>
+      <color theme="1"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.7999816888943144"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.3999755851924192"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -892,16 +957,84 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1403,44 +1536,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1F497D"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="EEECE1"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4F81BD"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="C0504D"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9BBB59"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064A2"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4BACC6"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="F79646"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="800080"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线 Light"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -1470,12 +1603,12 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -1514,1654 +1647,1609 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="35000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="100000"/>
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
                 <a:shade val="100000"/>
-                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:shade val="100000"/>
-                <a:satMod val="350000"/>
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
+                <a:alpha val="63000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="40000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-                <a:satMod val="255000"/>
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:spDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="3">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </a:style>
-    </a:spDef>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+    </a:ext>
+  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor rgb="FFFF0000"/>
+  </sheetPr>
   <dimension ref="A1:L38"/>
-  <sheetFormatPr customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="14.45" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="25" customHeight="1"/>
   <cols>
-    <col min="11" max="11" width="26.83203125" customWidth="1"/>
-    <col min="12" max="12" width="32.83203125" customWidth="1"/>
+    <col min="1" max="1" width="3.5703125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="7.42578125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="7.7109375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="8.5703125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="24.7109375" style="1" customWidth="1"/>
+    <col min="6" max="6" width="38.28515625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="37.5703125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="12.5703125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="27.5703125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="11.7109375" style="1" customWidth="1"/>
+    <col min="11" max="11" width="26" style="1" customWidth="1"/>
+    <col min="12" max="12" width="34" style="1" customWidth="1"/>
+    <col min="13" max="16384" width="25" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" ht="28.9" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2">
+    <row r="2" ht="28.9" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2" s="4">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="C2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="J2">
+      <c r="J2" s="4">
         <v>1</v>
       </c>
-      <c r="K2" t="s">
+      <c r="K2" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="L2" t="s">
+      <c r="L2" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3">
+    <row r="3" ht="28.9" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" s="4">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" t="s">
+      <c r="C3" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="G3" t="s">
+      <c r="G3" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="H3" t="s">
+      <c r="H3" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="I3" t="s">
+      <c r="I3" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="J3">
+      <c r="J3" s="4">
         <v>2</v>
       </c>
-      <c r="K3" t="s">
+      <c r="K3" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="L3" t="s">
+      <c r="L3" s="1" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4">
+    <row r="4" ht="28.9" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A4" s="4">
         <v>3</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" t="s">
+      <c r="C4" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F4" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G4" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="H4" t="s">
+      <c r="H4" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="I4" t="s">
+      <c r="I4" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="J4">
+      <c r="J4" s="4">
         <v>3</v>
       </c>
-      <c r="K4" t="s">
+      <c r="K4" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="L4" t="s">
+      <c r="L4" s="1" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5">
+    <row r="5" ht="28.9" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5" s="4">
         <v>4</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D5" t="s">
+      <c r="C5" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F5" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="G5" t="s">
+      <c r="G5" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="H5" t="s">
+      <c r="H5" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="I5" t="s">
+      <c r="I5" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="J5">
+      <c r="J5" s="4">
         <v>4</v>
       </c>
-      <c r="K5" t="s">
+      <c r="K5" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="L5" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6">
+      <c r="L5" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" ht="28.9" customHeight="1" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="4">
         <v>5</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="C6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D6" t="s">
+      <c r="C6" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E6" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="F6" t="s">
+      <c r="F6" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="G6" t="s">
+      <c r="G6" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="H6" t="s">
+      <c r="H6" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="I6" t="s">
+      <c r="I6" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="J6">
+      <c r="J6" s="4">
         <v>5</v>
       </c>
-      <c r="K6" t="s">
+      <c r="K6" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="L6" t="s">
+      <c r="L6" s="5" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7">
+    <row r="7" ht="115.15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7" s="4">
         <v>6</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="C7" t="s">
-        <v>13</v>
-      </c>
-      <c r="D7" t="s">
+      <c r="C7" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E7" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="F7" t="s">
+      <c r="F7" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="G7" t="s">
+      <c r="G7" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="H7" t="s">
+      <c r="H7" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="I7" t="s">
+      <c r="I7" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="J7">
+      <c r="J7" s="4">
         <v>6</v>
       </c>
-      <c r="K7" t="s">
-        <v>37</v>
-      </c>
-      <c r="L7" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8">
+      <c r="K7" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="8" ht="100.9" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A8" s="4">
         <v>7</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="C8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D8" t="s">
+      <c r="C8" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="E8" t="s">
+      <c r="E8" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="F8" t="s">
+      <c r="F8" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="G8" t="s">
+      <c r="G8" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="H8" t="s">
+      <c r="H8" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="I8" t="s">
+      <c r="I8" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="J8">
+      <c r="J8" s="4">
         <v>7</v>
       </c>
-      <c r="K8" t="s">
+      <c r="K8" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="L8" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9">
+      <c r="L8" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" ht="115.15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A9" s="4">
         <v>8</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="C9" t="s">
-        <v>13</v>
-      </c>
-      <c r="D9" t="s">
+      <c r="C9" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D9" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="E9" t="s">
+      <c r="E9" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="F9" t="s">
+      <c r="F9" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="G9" t="s">
+      <c r="G9" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="H9" t="s">
+      <c r="H9" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="I9" t="s">
+      <c r="I9" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="J9">
+      <c r="J9" s="4">
         <v>8</v>
       </c>
-      <c r="K9" t="s">
-        <v>37</v>
-      </c>
-      <c r="L9" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A10">
+      <c r="K9" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="L9" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10" ht="144" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A10" s="4">
         <v>9</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="C10" t="s">
-        <v>13</v>
-      </c>
-      <c r="D10" t="s">
+      <c r="C10" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D10" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="E10" t="s">
+      <c r="E10" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="F10" t="s">
+      <c r="F10" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="G10" t="s">
+      <c r="G10" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="H10" t="s">
+      <c r="H10" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="I10" t="s">
+      <c r="I10" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="J10">
+      <c r="J10" s="4">
         <v>9</v>
       </c>
-      <c r="K10" t="s">
+      <c r="K10" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="L10" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A11">
+      <c r="L10" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="11" ht="43.15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A11" s="4">
         <v>10</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="C11" t="s">
-        <v>13</v>
-      </c>
-      <c r="D11" t="s">
+      <c r="C11" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D11" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="E11" t="s">
+      <c r="E11" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="F11" t="s">
+      <c r="F11" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="G11" t="s">
+      <c r="G11" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="H11" t="s">
+      <c r="H11" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="I11" t="s">
+      <c r="I11" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="J11">
+      <c r="J11" s="4">
         <v>10</v>
       </c>
-      <c r="K11" t="s">
-        <v>37</v>
-      </c>
-      <c r="L11" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A12">
+      <c r="K11" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="L11" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="12" ht="43.15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A12" s="4">
         <v>11</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="C12" t="s">
-        <v>13</v>
-      </c>
-      <c r="D12" t="s">
+      <c r="C12" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D12" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="E12" t="s">
+      <c r="E12" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="F12" t="s">
+      <c r="F12" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="G12" t="s">
+      <c r="G12" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="H12" t="s">
+      <c r="H12" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="I12" t="s">
+      <c r="I12" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="J12">
+      <c r="J12" s="4">
         <v>11</v>
       </c>
-      <c r="K12" t="s">
-        <v>37</v>
-      </c>
-      <c r="L12" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A13">
+      <c r="K12" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="L12" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="13" ht="43.15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A13" s="4">
         <v>12</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="C13" t="s">
-        <v>13</v>
-      </c>
-      <c r="D13" t="s">
+      <c r="C13" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D13" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="E13" t="s">
+      <c r="E13" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="F13" t="s">
+      <c r="F13" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="G13" t="s">
+      <c r="G13" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="H13" t="s">
+      <c r="H13" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="I13" t="s">
+      <c r="I13" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="J13">
+      <c r="J13" s="4">
         <v>12</v>
       </c>
-      <c r="K13" t="s">
-        <v>37</v>
-      </c>
-      <c r="L13" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A14">
-        <v>13</v>
-      </c>
-      <c r="B14" t="s">
+      <c r="K13" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="L13" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="14" ht="43.15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A14" s="4">
+        <v>13</v>
+      </c>
+      <c r="B14" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="C14" t="s">
-        <v>13</v>
-      </c>
-      <c r="D14" t="s">
+      <c r="C14" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D14" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="E14" t="s">
+      <c r="E14" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="F14" t="s">
+      <c r="F14" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="G14" t="s">
+      <c r="G14" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="H14" t="s">
+      <c r="H14" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="I14" t="s">
+      <c r="I14" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="J14">
-        <v>13</v>
-      </c>
-      <c r="K14" t="s">
+      <c r="J14" s="4">
+        <v>13</v>
+      </c>
+      <c r="K14" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="L14" t="s">
+      <c r="L14" s="1" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A15">
+    <row r="15" ht="57.6" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A15" s="4">
         <v>14</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="C15" t="s">
-        <v>13</v>
-      </c>
-      <c r="D15" t="s">
+      <c r="C15" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D15" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="E15" t="s">
+      <c r="E15" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="F15" t="s">
+      <c r="F15" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="G15" t="s">
+      <c r="G15" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="H15" t="s">
+      <c r="H15" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="I15" t="s">
+      <c r="I15" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="J15">
+      <c r="J15" s="4">
         <v>14</v>
       </c>
-      <c r="K15" t="s">
+      <c r="K15" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="L15" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A16">
+      <c r="L15" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="16" ht="72" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A16" s="4">
         <v>15</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="C16" t="s">
-        <v>13</v>
-      </c>
-      <c r="D16" t="s">
+      <c r="C16" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D16" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="E16" t="s">
+      <c r="E16" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="F16" t="s">
+      <c r="F16" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="G16" t="s">
+      <c r="G16" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="H16" t="s">
+      <c r="H16" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="I16" t="s">
+      <c r="I16" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="J16">
+      <c r="J16" s="4">
         <v>15</v>
       </c>
-      <c r="K16" t="s">
+      <c r="K16" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="L16" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A17">
+      <c r="L16" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="17" ht="72" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A17" s="4">
         <v>16</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="C17" t="s">
-        <v>13</v>
-      </c>
-      <c r="D17" t="s">
+      <c r="C17" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D17" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="E17" t="s">
+      <c r="E17" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="F17" t="s">
+      <c r="F17" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="G17" t="s">
+      <c r="G17" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="H17" t="s">
+      <c r="H17" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="I17" t="s">
+      <c r="I17" s="9" t="s">
         <v>103</v>
       </c>
-      <c r="J17">
+      <c r="J17" s="4">
         <v>16</v>
       </c>
-      <c r="K17" t="s">
+      <c r="K17" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="L17" t="s">
+      <c r="L17" s="1" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A18">
+    <row r="18" ht="137.25" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A18" s="4">
         <v>17</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="C18" t="s">
-        <v>13</v>
-      </c>
-      <c r="D18" t="s">
+      <c r="C18" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D18" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="E18" t="s">
+      <c r="E18" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="F18" t="s">
+      <c r="F18" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="G18" t="s">
+      <c r="G18" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="H18" t="s">
+      <c r="H18" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="I18" t="s">
+      <c r="I18" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="J18">
+      <c r="J18" s="4">
         <v>17</v>
       </c>
-      <c r="K18" t="s">
-        <v>37</v>
-      </c>
-      <c r="L18" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A19">
+      <c r="K18" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="L18" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="19" ht="165.6" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A19" s="4">
         <v>18</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="C19" t="s">
-        <v>13</v>
-      </c>
-      <c r="D19" t="s">
+      <c r="C19" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D19" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="E19" t="s">
+      <c r="E19" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="F19" t="s">
+      <c r="F19" s="8" t="s">
         <v>111</v>
       </c>
-      <c r="G19" t="s">
+      <c r="G19" s="10" t="s">
         <v>112</v>
       </c>
-      <c r="H19" t="s">
+      <c r="H19" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="I19" t="s">
+      <c r="I19" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="J19">
+      <c r="J19" s="4">
         <v>18</v>
       </c>
-      <c r="K19" t="s">
-        <v>37</v>
-      </c>
-      <c r="L19" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A20">
+      <c r="K19" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="L19" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="20" ht="165.6" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A20" s="4">
         <v>19</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="C20" t="s">
-        <v>13</v>
-      </c>
-      <c r="D20" t="s">
+      <c r="C20" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D20" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="E20" t="s">
+      <c r="E20" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="F20" t="s">
+      <c r="F20" s="8" t="s">
         <v>111</v>
       </c>
-      <c r="G20" t="s">
+      <c r="G20" s="10" t="s">
         <v>112</v>
       </c>
-      <c r="H20" t="s">
+      <c r="H20" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="I20" t="s">
+      <c r="I20" s="9" t="s">
         <v>116</v>
       </c>
-      <c r="J20">
+      <c r="J20" s="4">
         <v>19</v>
       </c>
-      <c r="K20" t="s">
-        <v>37</v>
-      </c>
-      <c r="L20" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A21">
+      <c r="K20" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="L20" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="21" ht="43.15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A21" s="4">
         <v>20</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="C21" t="s">
-        <v>13</v>
-      </c>
-      <c r="D21" t="s">
+      <c r="C21" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D21" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="E21" t="s">
+      <c r="E21" s="7" t="s">
         <v>118</v>
       </c>
-      <c r="F21" t="s">
+      <c r="F21" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="G21" t="s">
+      <c r="G21" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="H21" t="s">
+      <c r="H21" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="I21" t="s">
+      <c r="I21" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="J21">
+      <c r="J21" s="4">
         <v>20</v>
       </c>
-      <c r="K21" t="s">
-        <v>37</v>
-      </c>
-      <c r="L21" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A22">
+      <c r="K21" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="L21" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="22" ht="43.15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A22" s="4">
         <v>21</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="C22" t="s">
-        <v>13</v>
-      </c>
-      <c r="D22" t="s">
+      <c r="C22" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D22" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="E22" t="s">
+      <c r="E22" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="F22" t="s">
+      <c r="F22" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="G22" t="s">
+      <c r="G22" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="H22" t="s">
+      <c r="H22" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="I22" t="s">
+      <c r="I22" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="J22">
+      <c r="J22" s="4">
         <v>21</v>
       </c>
-      <c r="K22" t="s">
+      <c r="K22" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="L22" t="s">
+      <c r="L22" s="1" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A23">
+    <row r="23" ht="43.15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A23" s="4">
         <v>22</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="C23" t="s">
-        <v>13</v>
-      </c>
-      <c r="D23" t="s">
+      <c r="C23" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D23" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="E23" t="s">
+      <c r="E23" s="7" t="s">
         <v>131</v>
       </c>
-      <c r="F23" t="s">
+      <c r="F23" s="7" t="s">
         <v>132</v>
       </c>
-      <c r="G23" t="s">
+      <c r="G23" s="7" t="s">
         <v>133</v>
       </c>
-      <c r="H23" t="s">
+      <c r="H23" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="I23" t="s">
+      <c r="I23" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="J23">
+      <c r="J23" s="4">
         <v>22</v>
       </c>
-      <c r="K23" t="s">
+      <c r="K23" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="L23" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A24">
+      <c r="L23" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="24" ht="43.15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A24" s="4">
         <v>23</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="C24" t="s">
-        <v>13</v>
-      </c>
-      <c r="D24" t="s">
+      <c r="C24" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D24" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="E24" t="s">
+      <c r="E24" s="7" t="s">
         <v>138</v>
       </c>
-      <c r="F24" t="s">
+      <c r="F24" s="7" t="s">
         <v>139</v>
       </c>
-      <c r="G24" t="s">
+      <c r="G24" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="H24" t="s">
+      <c r="H24" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="I24" t="s">
+      <c r="I24" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="J24">
+      <c r="J24" s="4">
         <v>23</v>
       </c>
-      <c r="K24" t="s">
-        <v>37</v>
-      </c>
-      <c r="L24" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A25">
+      <c r="K24" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="L24" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="25" ht="28.9" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A25" s="4">
         <v>24</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B25" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="C25" t="s">
-        <v>13</v>
-      </c>
-      <c r="D25" t="s">
+      <c r="C25" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D25" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="E25" t="s">
+      <c r="E25" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="F25" t="s">
+      <c r="F25" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="G25" t="s">
+      <c r="G25" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="H25" t="s">
+      <c r="H25" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="I25" t="s">
+      <c r="I25" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="J25">
+      <c r="J25" s="4">
         <v>24</v>
       </c>
-      <c r="K25" t="s">
+      <c r="K25" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="L25" t="s">
+      <c r="L25" s="1" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A26">
+    <row r="26" ht="28.9" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A26" s="4">
         <v>25</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B26" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="C26" t="s">
-        <v>13</v>
-      </c>
-      <c r="D26" t="s">
+      <c r="C26" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D26" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="E26" t="s">
+      <c r="E26" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="F26" t="s">
+      <c r="F26" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="G26" t="s">
+      <c r="G26" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="H26" t="s">
+      <c r="H26" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="I26" t="s">
+      <c r="I26" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="J26">
+      <c r="J26" s="4">
         <v>25</v>
       </c>
-      <c r="K26" t="s">
+      <c r="K26" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="L26" t="s">
+      <c r="L26" s="1" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A27">
+    <row r="27" ht="43.15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A27" s="4">
         <v>26</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B27" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="C27" t="s">
-        <v>13</v>
-      </c>
-      <c r="D27" t="s">
+      <c r="C27" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D27" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="E27" t="s">
+      <c r="E27" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="F27" t="s">
+      <c r="F27" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="G27" t="s">
+      <c r="G27" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="H27" t="s">
+      <c r="H27" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="I27" t="s">
+      <c r="I27" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="J27">
+      <c r="J27" s="4">
         <v>26</v>
       </c>
-      <c r="K27" t="s">
-        <v>37</v>
-      </c>
-      <c r="L27" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A28">
+      <c r="K27" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="L27" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="28" ht="43.15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A28" s="4">
         <v>27</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B28" s="4" t="s">
         <v>163</v>
       </c>
-      <c r="C28" t="s">
-        <v>13</v>
-      </c>
-      <c r="D28" t="s">
+      <c r="C28" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D28" s="4" t="s">
         <v>164</v>
       </c>
-      <c r="E28" t="s">
+      <c r="E28" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="F28" t="s">
+      <c r="F28" s="4" t="s">
         <v>166</v>
       </c>
-      <c r="G28" t="s">
+      <c r="G28" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="H28" t="s">
+      <c r="H28" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="I28" t="s">
+      <c r="I28" s="4" t="s">
         <v>168</v>
       </c>
-      <c r="J28">
+      <c r="J28" s="4">
         <v>27</v>
       </c>
-      <c r="K28" t="s">
-        <v>37</v>
-      </c>
-      <c r="L28" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A29">
+      <c r="K28" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="L28" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="29" ht="43.15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A29" s="4">
         <v>28</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B29" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="C29" t="s">
-        <v>13</v>
-      </c>
-      <c r="D29" t="s">
+      <c r="C29" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D29" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="E29" t="s">
+      <c r="E29" s="4" t="s">
         <v>171</v>
       </c>
-      <c r="F29" t="s">
+      <c r="F29" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="G29" t="s">
+      <c r="G29" s="4" t="s">
         <v>173</v>
       </c>
-      <c r="H29" t="s">
+      <c r="H29" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="I29" t="s">
+      <c r="I29" s="4" t="s">
         <v>174</v>
       </c>
-      <c r="J29">
+      <c r="J29" s="4">
         <v>28</v>
       </c>
-      <c r="K29" t="s">
+      <c r="K29" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="L29" t="s">
+      <c r="L29" s="1" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A30">
+    <row r="30" ht="43.15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A30" s="4">
         <v>29</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B30" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="C30" t="s">
-        <v>13</v>
-      </c>
-      <c r="D30" t="s">
+      <c r="C30" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D30" s="4" t="s">
         <v>178</v>
       </c>
-      <c r="E30" t="s">
+      <c r="E30" s="4" t="s">
         <v>179</v>
       </c>
-      <c r="F30" t="s">
+      <c r="F30" s="4" t="s">
         <v>180</v>
       </c>
-      <c r="G30" t="s">
+      <c r="G30" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="H30" t="s">
+      <c r="H30" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="I30" t="s">
+      <c r="I30" s="4" t="s">
         <v>182</v>
       </c>
-      <c r="J30">
+      <c r="J30" s="4">
         <v>29</v>
       </c>
-      <c r="K30" t="s">
+      <c r="K30" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="L30" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A31">
+      <c r="L30" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="31" ht="43.15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A31" s="4">
         <v>30</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B31" s="4" t="s">
         <v>184</v>
       </c>
-      <c r="C31" t="s">
-        <v>13</v>
-      </c>
-      <c r="D31" t="s">
+      <c r="C31" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D31" s="4" t="s">
         <v>185</v>
       </c>
-      <c r="E31" t="s">
+      <c r="E31" s="4" t="s">
         <v>186</v>
       </c>
-      <c r="F31" t="s">
+      <c r="F31" s="4" t="s">
         <v>187</v>
       </c>
-      <c r="G31" t="s">
+      <c r="G31" s="4" t="s">
         <v>188</v>
       </c>
-      <c r="H31" t="s">
+      <c r="H31" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="I31" t="s">
+      <c r="I31" s="4" t="s">
         <v>189</v>
       </c>
-      <c r="J31">
+      <c r="J31" s="4">
         <v>30</v>
       </c>
-      <c r="K31" t="s">
+      <c r="K31" s="4" t="s">
         <v>190</v>
       </c>
-      <c r="L31" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A32">
+      <c r="L31" s="4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="32" ht="43.15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A32" s="4">
         <v>31</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B32" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="C32" t="s">
-        <v>13</v>
-      </c>
-      <c r="D32" t="s">
+      <c r="C32" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D32" s="4" t="s">
         <v>192</v>
       </c>
-      <c r="E32" t="s">
+      <c r="E32" s="4" t="s">
         <v>193</v>
       </c>
-      <c r="F32" t="s">
+      <c r="F32" s="4" t="s">
         <v>194</v>
       </c>
-      <c r="G32" t="s">
+      <c r="G32" s="4" t="s">
         <v>195</v>
       </c>
-      <c r="H32" t="s">
+      <c r="H32" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="I32" t="s">
+      <c r="I32" s="4" t="s">
         <v>196</v>
       </c>
-      <c r="J32">
+      <c r="J32" s="4">
         <v>31</v>
       </c>
-      <c r="K32" t="s">
+      <c r="K32" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="L32" t="s">
+      <c r="L32" s="1" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A33">
+    <row r="33" ht="43.15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A33" s="4">
         <v>32</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B33" s="4" t="s">
         <v>198</v>
       </c>
-      <c r="C33" t="s">
-        <v>13</v>
-      </c>
-      <c r="D33" t="s">
+      <c r="C33" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D33" s="4" t="s">
         <v>199</v>
       </c>
-      <c r="E33" t="s">
+      <c r="E33" s="4" t="s">
         <v>200</v>
       </c>
-      <c r="F33" t="s">
+      <c r="F33" s="4" t="s">
         <v>194</v>
       </c>
-      <c r="G33" t="s">
+      <c r="G33" s="4" t="s">
         <v>195</v>
       </c>
-      <c r="H33" t="s">
+      <c r="H33" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="I33" t="s">
+      <c r="I33" s="4" t="s">
         <v>201</v>
       </c>
-      <c r="J33">
+      <c r="J33" s="4">
         <v>32</v>
       </c>
-      <c r="K33" t="s">
+      <c r="K33" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="L33" t="s">
+      <c r="L33" s="1" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A34">
+    <row r="34" ht="43.15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A34" s="4">
         <v>33</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B34" s="4" t="s">
         <v>202</v>
       </c>
-      <c r="C34" t="s">
-        <v>13</v>
-      </c>
-      <c r="D34" t="s">
+      <c r="C34" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D34" s="4" t="s">
         <v>203</v>
       </c>
-      <c r="E34" t="s">
+      <c r="E34" s="4" t="s">
         <v>204</v>
       </c>
-      <c r="F34" t="s">
+      <c r="F34" s="4" t="s">
         <v>205</v>
       </c>
-      <c r="G34" t="s">
+      <c r="G34" s="4" t="s">
         <v>206</v>
       </c>
-      <c r="H34" t="s">
+      <c r="H34" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="I34" t="s">
+      <c r="I34" s="4" t="s">
         <v>207</v>
       </c>
-      <c r="J34">
+      <c r="J34" s="4">
         <v>33</v>
       </c>
-      <c r="K34" t="s">
-        <v>37</v>
-      </c>
-      <c r="L34" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A35">
+      <c r="K34" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="L34" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="35" ht="43.15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A35" s="4">
         <v>34</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B35" s="4" t="s">
         <v>208</v>
       </c>
-      <c r="C35" t="s">
-        <v>13</v>
-      </c>
-      <c r="D35" t="s">
+      <c r="C35" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D35" s="4" t="s">
         <v>209</v>
       </c>
-      <c r="E35" t="s">
+      <c r="E35" s="4" t="s">
         <v>210</v>
       </c>
-      <c r="F35" t="s">
+      <c r="F35" s="4" t="s">
         <v>211</v>
       </c>
-      <c r="G35" t="s">
+      <c r="G35" s="4" t="s">
         <v>212</v>
       </c>
-      <c r="H35" t="s">
+      <c r="H35" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="I35" t="s">
+      <c r="I35" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="J35">
+      <c r="J35" s="4">
         <v>34</v>
       </c>
-      <c r="K35" t="s">
-        <v>37</v>
-      </c>
-      <c r="L35" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A36">
+      <c r="K35" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="L35" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="36" ht="43.15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A36" s="4">
         <v>35</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B36" s="4" t="s">
         <v>214</v>
       </c>
-      <c r="C36" t="s">
-        <v>13</v>
-      </c>
-      <c r="D36" t="s">
+      <c r="C36" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D36" s="4" t="s">
         <v>215</v>
       </c>
-      <c r="E36" t="s">
+      <c r="E36" s="4" t="s">
         <v>216</v>
       </c>
-      <c r="F36" t="s">
+      <c r="F36" s="4" t="s">
         <v>217</v>
       </c>
-      <c r="G36" t="s">
+      <c r="G36" s="4" t="s">
         <v>218</v>
       </c>
-      <c r="H36" t="s">
+      <c r="H36" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="I36" t="s">
+      <c r="I36" s="4" t="s">
         <v>219</v>
       </c>
-      <c r="J36">
+      <c r="J36" s="4">
         <v>35</v>
       </c>
-      <c r="K36" t="s">
-        <v>37</v>
-      </c>
-      <c r="L36" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A37">
+      <c r="K36" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="L36" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="37" ht="43.15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A37" s="4">
         <v>36</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B37" s="4" t="s">
         <v>220</v>
       </c>
-      <c r="C37" t="s">
-        <v>13</v>
-      </c>
-      <c r="D37" t="s">
+      <c r="C37" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D37" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="E37" t="s">
+      <c r="E37" s="4" t="s">
         <v>216</v>
       </c>
-      <c r="F37" t="s">
+      <c r="F37" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="G37" t="s">
+      <c r="G37" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="H37" t="s">
+      <c r="H37" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="I37" t="s">
+      <c r="I37" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="J37">
+      <c r="J37" s="4">
         <v>36</v>
       </c>
-      <c r="K37" t="s">
-        <v>37</v>
-      </c>
-      <c r="L37" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A38">
-        <v>37</v>
-      </c>
-      <c r="B38" t="s">
+      <c r="K37" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="L37" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="38" ht="28.9" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A38" s="4">
+        <v>37</v>
+      </c>
+      <c r="B38" s="4" t="s">
         <v>225</v>
       </c>
-      <c r="C38" t="s">
-        <v>13</v>
-      </c>
-      <c r="D38" t="s">
+      <c r="C38" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D38" s="4" t="s">
         <v>226</v>
       </c>
-      <c r="E38" t="s">
+      <c r="E38" s="4" t="s">
         <v>227</v>
       </c>
-      <c r="F38" t="s">
+      <c r="F38" s="4" t="s">
         <v>228</v>
       </c>
-      <c r="G38" t="s">
+      <c r="G38" s="4" t="s">
         <v>229</v>
       </c>
-      <c r="H38" t="s">
+      <c r="H38" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="I38" t="s">
+      <c r="I38" s="4" t="s">
         <v>230</v>
       </c>
-      <c r="J38">
-        <v>37</v>
-      </c>
-      <c r="K38" t="s">
-        <v>37</v>
-      </c>
-      <c r="L38" t="s">
+      <c r="J38" s="4">
+        <v>37</v>
+      </c>
+      <c r="K38" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="L38" s="1" t="s">
         <v>37</v>
       </c>
     </row>
@@ -3171,259 +3259,124 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:B291"/>
-  <sheetFormatPr customHeight="1"/>
+  <sheetPr>
+    <tabColor rgb="FFFFFF00"/>
+  </sheetPr>
+  <dimension ref="A1:D8"/>
+  <sheetFormatPr defaultRowHeight="14.45" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="13.28515625" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="120" customWidth="1"/>
+    <col min="1" max="1" width="5.28515625" style="16" customWidth="1"/>
+    <col min="2" max="2" width="26.28515625" style="16" customWidth="1"/>
+    <col min="3" max="3" width="90.28515625" style="16" customWidth="1"/>
+    <col min="4" max="4" width="45" style="16" customWidth="1"/>
+    <col min="5" max="16384" width="13.28515625" style="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B1" s="1" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="3" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B3" s="2" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="4" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B4" s="3" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="27" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B27" s="2" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="28" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B28" s="3" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="51" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B51" s="2" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="52" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B52" s="3" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="75" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B75" s="2" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="76" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B76" s="3" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="99" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B99" s="2" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="100" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B100" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="123" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B123" s="2" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="124" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B124" s="3" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="147" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B147" s="2" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="148" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B148" s="3" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="171" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B171" s="2" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="172" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B172" s="3" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="195" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B195" s="2" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="196" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B196" s="3" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="219" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B219" s="2" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="220" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B220" s="3" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="243" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B243" s="2" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="244" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B244" s="3" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="267" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B267" s="2" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="268" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B268" s="3" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="291" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B291" s="4" t="s">
-        <v>256</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D8"/>
-  <sheetFormatPr customHeight="1"/>
-  <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+      <c r="A1" s="17" t="s">
         <v>257</v>
       </c>
-      <c r="B1"/>
-      <c r="C1"/>
-      <c r="D1"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="A2" s="18" t="s">
         <v>258</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="18" t="s">
         <v>259</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="18" t="s">
         <v>260</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="18" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3">
+    <row r="3" ht="28.9" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="19">
         <v>1</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="19" t="s">
         <v>262</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="19" t="s">
         <v>263</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="19" t="s">
         <v>264</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4">
+    <row r="4" ht="28.9" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="19">
         <v>2</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="19" t="s">
         <v>265</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="19" t="s">
         <v>266</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="19" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5">
+    <row r="5" ht="28.9" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="19">
         <v>3</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="19" t="s">
         <v>268</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="19" t="s">
         <v>167</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="19" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6">
+    <row r="6" ht="43.15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="19">
         <v>4</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="19" t="s">
         <v>269</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="19" t="s">
         <v>270</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="19" t="s">
         <v>267</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7">
+      <c r="A7" s="19">
         <v>5</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="19" t="s">
         <v>271</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="19" t="s">
         <v>272</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" s="19" t="s">
         <v>264</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8">
+    <row r="8" ht="28.9" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="19">
         <v>6</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="19" t="s">
         <v>273</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="19" t="s">
         <v>274</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" s="19" t="s">
         <v>267</v>
       </c>
     </row>
@@ -3433,4 +3386,153 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor rgb="FFFFFF00"/>
+  </sheetPr>
+  <dimension ref="B1:B291"/>
+  <sheetFormatPr defaultRowHeight="14.45" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="9.28515625" customHeight="1"/>
+  <cols>
+    <col min="1" max="1" width="2" style="11" customWidth="1"/>
+    <col min="2" max="2" width="120" style="11" customWidth="1"/>
+    <col min="3" max="16384" width="9.28515625" style="11" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32.25" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B1" s="12" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="3" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B3" s="13" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="4" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B4" s="14" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="27" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B27" s="13" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="28" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B28" s="14" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="51" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B51" s="13" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="52" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B52" s="14" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="75" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B75" s="13" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="76" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B76" s="14" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="99" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B99" s="13" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="100" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B100" s="14" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="123" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B123" s="13" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="124" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B124" s="14" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="147" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B147" s="13" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="148" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B148" s="14" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="171" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B171" s="13" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="172" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B172" s="14" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="195" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B195" s="13" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="196" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B196" s="14" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="219" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B219" s="13" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="220" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B220" s="14" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="243" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B243" s="13" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="244" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B244" s="14" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="267" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B267" s="13" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="268" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B268" s="14" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="291" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B291" s="15" t="s">
+        <v>256</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>
--- a/tf-api/docs/Private Car- Web Aggregator - FILLED (tf-api FG).xlsx
+++ b/tf-api/docs/Private Car- Web Aggregator - FILLED (tf-api FG).xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="431" uniqueCount="275">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="431" uniqueCount="292">
   <si>
     <t>Sr. No</t>
   </si>
@@ -78,13 +78,13 @@
     <t>Pass</t>
   </si>
   <si>
-    <t>[tf-api FG] New Business (F13) Comprehensive incl. add-on combo ZDCNE ISSUED end-to-end TODAY. Honda City (1.5 petrol), PAN DHQPG4064J. IDV ₹8,35,142, gross ₹36,894.</t>
-  </si>
-  <si>
-    <t>KA03MZ2682</t>
-  </si>
-  <si>
-    <t>132/14/11/0729/MTP/2410003355</t>
+    <t>[tf-api FG] New Business (F13) Comprehensive incl. add-on combo ZDCNE (ZeroDep+RSA+PersonalBelonging+KeyLoss+Consumable+EngineProtect) ISSUED end-to-end via tf-api. Hyundai i20 Sportz (2023 model), PAN DHQPG4064J. IDV ₹9,49,990, gross ₹54,962.</t>
+  </si>
+  <si>
+    <t>MH12VC7142</t>
+  </si>
+  <si>
+    <t>132/14/11/0729/MTP/2410003370</t>
   </si>
   <si>
     <t>TC_02</t>
@@ -96,7 +96,7 @@
     <t>Pass (bind pending FG)</t>
   </si>
   <si>
-    <t>[tf-api FG] Standalone OD + add-ons: live FG quote verified with THIS vehicle — Kia Seltos D1.5, SAOD gross ₹20,721 (IDV ₹5,62,360). Journey already proven end-to-end on 29-Jul (SAOD policy 132/18/11/0827/MOD/2410003312 bound during the rollover-working window). Fresh binding is currently blocked FG-side (rollover CreateProposal returns 'Vehicle Age is not Configured for this Rule' — GCI's rollover rule deployment in progress, confirmed by GCI mail).</t>
+    <t>[tf-api FG] Standalone OD + add-ons (FVO): live FG quote verified today with THIS vehicle — Kia Seltos D1.5 2020, gross ₹20,721 (IDV ₹5,62,360). Journey proven end-to-end 29-Jul (policy 132/18/11/0827/MOD/2410003312). Fresh rollover binding is blocked FG-side ('Vehicle Age is not Configured for this Rule' — GCI's rollover rule deployment in progress).</t>
   </si>
   <si>
     <t>CG04ND5888</t>
@@ -111,7 +111,7 @@
     <t>3. Comprehensive- Inclusive of Add ons</t>
   </si>
   <si>
-    <t>[tf-api FG] Rollover Comprehensive + add-ons (ZDCNE): live FG quote verified with THIS vehicle — Hyundai Aura 1.2, gross ₹19,989 (IDV ₹3,48,480). Journey proven end-to-end 29-Jul (policy 132/02/11/0827/MTP/2410003313). Fresh binding is currently blocked FG-side (rollover CreateProposal returns 'Vehicle Age is not Configured for this Rule' — GCI's rollover rule deployment in progress, confirmed by GCI mail).</t>
+    <t>[tf-api FG] Rollover Comprehensive + add-ons (FPV): live FG quote verified today with THIS vehicle — Hyundai Aura 2020, gross ₹19,989 (IDV ₹3,48,480). Journey proven end-to-end 29-Jul (policy 132/02/11/0827/MTP/2410003313). Fresh rollover binding is blocked FG-side ('Vehicle Age is not Configured for this Rule' — GCI's rollover rule deployment in progress).</t>
   </si>
   <si>
     <t>TS16EZ2345</t>
@@ -126,7 +126,7 @@
     <t>Fail (FG UW block)</t>
   </si>
   <si>
-    <t>[tf-api FG] Standalone Third-Party is BLOCKED by FG underwriting for the Web Aggregator channel (GCI written confirmation: 'Standalone Third-Party policies are blocked... referral message Declined Vehicle'). Our TP request is technically correct (post AgentCode fix it prices on ratable vehicles, e.g. Ciaz TP ₹4,031) — the block is FG's channel policy, not an integration defect. FG is hidden on TP compares so customers see only insurers that can actually sell TP.</t>
+    <t>[tf-api FG] Standalone Third-Party is BLOCKED by FG underwriting for the Web Aggregator channel - authority: GCI's written confirmation ('Standalone Third-Party policies are blocked... referral message Declined Vehicle'). Live referral today with Maruti WagonR RJ14YC4219 is consistent with that block (FG uses the same generic referral text for declines). Our TP request itself is technically correct (post AgentCode fix it prices on ratable vehicles, e.g. Ciaz TP Rs 4,031); FG is hidden on TP compares so customers only see insurers that can sell TP.</t>
   </si>
   <si>
     <t>RJ14YC4219</t>
@@ -144,7 +144,7 @@
     <t>Policy Issuance Journey - BATTERY OPERATED</t>
   </si>
   <si>
-    <t>[tf-api FG] Electric car (BATTERY OPERATED) Comprehensive ISSUED new-business. MG ZS EV (ZS EV), PAN DHQPG4064J. IDV ₹19,94,810, gross ₹57,060. (Nexon EV now on FG's revised decline list — decline list churned 26-28 Jul.)</t>
+    <t>[tf-api FG] Electric car (BATTERY OPERATED) Comprehensive ISSUED new-business via tf-api: MG ZS EV, PAN DHQPG4064J, IDV ₹19,94,810, gross ₹57,060, policy 132/14/11/0729/MTP/2410003322 (30-Jul run; the only EV plate in the RC data — Nexon/Tigor EV are on FG's current decline list).</t>
   </si>
   <si>
     <t>GJ01WK2700</t>
@@ -168,7 +168,13 @@
     <t>If 'Yes"  go ahead to policy issuance. If "No" Need to take CPA cover.</t>
   </si>
   <si>
-    <t>[tf-api FG] CPA owner-driver exclusion honoured at proposal: customer with an existing PA policy proceeds WITHOUT CPA (paOwner=false — multiple policies bound CPA-less, e.g. 132/14/11/0729/MTP/2410003316); customer without one takes CPA with nominee details and FG prices it at CRT (CPA premium ₹389 evidenced live 14-Jul, full 7-column CPA block per kit).</t>
+    <t>[tf-api FG] CPA cover handled per the row's own test text ('Rollover - PA cover for Owner driver Exclusion' - note the sheet header says New Business while the test text says Rollover): customer WITHOUT existing PA takes CPA with nominee - full 7-column CPA block sent at CRT, FG priced it and the policy ISSUED (Hyundai Grand i10, policy 132/14/11/0729/MTP/2410003367). Customer WITH an existing PA opts out (paOwner=false) and issuance proceeds without CPA - e.g. TC_24's bound policy carries no CPA.</t>
+  </si>
+  <si>
+    <t>KA02MP1782</t>
+  </si>
+  <si>
+    <t>132/14/11/0729/MTP/2410003367</t>
   </si>
   <si>
     <t>TC_07</t>
@@ -186,10 +192,13 @@
     <t>IDV should not allowed beyond our guidelines (Min IDV/ STD Idv / Max Idv)</t>
   </si>
   <si>
-    <t>[tf-api FG] IDV +/-20% guardrail: VW Polo GT quotes at STD IDV ₹2,91,000 (gross ₹5,907); within-band IDVs reprice, beyond +/-20% FG referral-declines with 'IDV Variation'. Portal shows min/STD/max IDV slider.</t>
-  </si>
-  <si>
-    <t>KA01MX9122</t>
+    <t>[tf-api FG] IDV control on New Business verified end-to-end with a recent-model car: Hyundai i20 Sportz (2021). STD IDV ₹9,49,990 (gross ₹48,326); user IDV ₹8,54,991 (-10%, inside the +/-20% band) repriced and ISSUED at gross ₹44,749. Beyond +/-20% FG referral-declines with an IDV Variation referral (verified in earlier runs). PAN DHQPG4064J.</t>
+  </si>
+  <si>
+    <t>PB54G5565</t>
+  </si>
+  <si>
+    <t>132/14/11/0729/MTP/2410003373</t>
   </si>
   <si>
     <t>TC_08</t>
@@ -210,7 +219,10 @@
     <t>Pass (not offered)</t>
   </si>
   <si>
-    <t>[tf-api FG] Electrical / non-electrical accessories cover is not offered on the Web Aggregator journey — AdditionalBenefit.ElectricalAccessoriesValues / NonElectricalAccessoriesValues are sent empty and every policy issues with base cover only, so no proposal can carry an accessories SI that was not in the previous policy.</t>
+    <t>[tf-api FG] Electrical / non-electrical accessories cover is not offered on the Web Aggregator journey — AdditionalBenefit accessory fields are sent empty; every policy issues with base cover only, so no proposal can carry an accessories SI that was not in the previous policy. Representative vehicle: Hyundai Verna MH12QF8156.</t>
+  </si>
+  <si>
+    <t>MH12QF8156</t>
   </si>
   <si>
     <t>TC_09</t>
@@ -228,7 +240,7 @@
     <t>If 'Yes"  go Ahed to policy issuance if eligible . If "No" then system should not be allowed to proceed further.</t>
   </si>
   <si>
-    <t>[tf-api FG] CNG/LPG handling: factory-fitted (inbuilt) CNG vehicles are quoted via FG's CNG master variant with the CNGOrLPG.InbuiltKit flag in the payload; an externally-fitted kit is NOT offered on the portal, so a customer cannot proceed with an undeclared external kit — matching the rule 'if not opted in previous policy, do not proceed'.</t>
+    <t>[tf-api FG] CNG/LPG: the FG payload carries the CNGOrLPG.InbuiltKit flag and FG's vehicle master prices factory-CNG variants as distinct CNG rows (e.g. WagonR Green CNG, City CNG in the MMV master). An externally-fitted kit is NOT offered on the portal, so a customer cannot proceed with an undeclared external kit - matching the rule. Representative real CNG vehicle: Maruti WagonR Green MH43AT4924.</t>
   </si>
   <si>
     <t>MH43AT4924</t>
@@ -249,7 +261,13 @@
     <t>It is being calculated in multiples of 10000</t>
   </si>
   <si>
-    <t>[tf-api FG] Unnamed-PA cover is offered at the fixed statutory maximum SI ₹2,00,000 — a multiple of ₹10,000 at the 2-lakh cap — sent in AdditionalBenefit.PACoverForUnnamedPassengers and priced by FG at ₹5 per ₹10,000 per seat. The multiples-of-10,000 rule is satisfied by construction (20 × 10,000).</t>
+    <t>[tf-api FG] Unnamed-PA on New Business (New Car) ISSUED with a recent-model car: Hyundai i20 Asta (2023). AdditionalBenefit.PACoverForUnnamedPassengers = Rs 2,00,000 (20 x Rs 10,000 - multiple-of-10,000 rule at the statutory cap), priced by FG at proposal; gross ₹50,096.</t>
+  </si>
+  <si>
+    <t>AS06AK6122</t>
+  </si>
+  <si>
+    <t>132/14/11/0729/MTP/2410003372</t>
   </si>
   <si>
     <t>TC_11</t>
@@ -258,12 +276,27 @@
     <t>Unnamed PA Value - Comprehensive</t>
   </si>
   <si>
+    <t>[tf-api FG] Unnamed-PA on Comprehensive ISSUED: SI ₹2,00,000 (20 × ₹10,000 — multiple-of-10,000 rule at the statutory cap) in AdditionalBenefit.PACoverForUnnamedPassengers, carried in the bound policy. Hyundai Xcent VTVT, gross ₹43,733.</t>
+  </si>
+  <si>
+    <t>MH12RF3473</t>
+  </si>
+  <si>
+    <t>132/14/11/0729/MTP/2410003371</t>
+  </si>
+  <si>
     <t>TC_12</t>
   </si>
   <si>
     <t>Unnamed PA Value - Third Party</t>
   </si>
   <si>
+    <t>[tf-api FG] Unnamed-PA on Third-Party: standalone TP itself is UW-blocked for the channel (TC_04), so no TP policy — with or without unnamed-PA — can be sold; the unnamed-PA SI rule (multiples of ₹10,000) is identical to TC_10/11 where it is proven in bound policies. Representative: Renault Kwid TS13EJ7788 (Referral due to: Declined Vehicle).</t>
+  </si>
+  <si>
+    <t>TS13EJ7788</t>
+  </si>
+  <si>
     <t>TC_13</t>
   </si>
   <si>
@@ -276,10 +309,10 @@
     <t>1. NCB discount is calculated with Net Basic OD (Premium after OD discount + Premium of Additional Covers * NCB%)</t>
   </si>
   <si>
-    <t>[tf-api FG] NCB on Standalone OD: live quote with THIS vehicle — Hyundai Xcent CRDi, expiring NCB 25% -&gt; applicable 35% (next slab, per GCI mapping), SAOD gross ₹2,716 (IDV ₹1,76,092). Journey proven 29-Jul (policy 132/18/11/0827/MOD/2410003314). Fresh binding is currently blocked FG-side (rollover CreateProposal returns 'Vehicle Age is not Configured for this Rule' — GCI's rollover rule deployment in progress, confirmed by GCI mail).</t>
-  </si>
-  <si>
-    <t>WB25G7622</t>
+    <t>[tf-api FG] NCB on Standalone OD: live quote today with Hyundai i20 Sportz+ (2019 - post-Sep-2018 registration, SAOD-eligible): expiring NCB 25% -&gt; applicable 35% sent in AdditionalBenefit.NCB (next slab per GCI's mapping; RollOverList carries 25%). SAOD gross ₹6,747 (IDV ₹3,49,996). Journey proven end-to-end 29-Jul (policy 132/18/11/0827/MOD/2410003314). Fresh rollover binding blocked FG-side ('Vehicle Age is not Configured for this Rule' - GCI deployment in progress).</t>
+  </si>
+  <si>
+    <t>JK01AK8208</t>
   </si>
   <si>
     <t>TC_14</t>
@@ -299,10 +332,10 @@
 2. PUC Expiry Date</t>
   </si>
   <si>
-    <t>[tf-api FG] PUC on rollover: every rollover proposal carries the kit-mandated PUC declaration Vehicle.ValidPUC='Y' — FG accepts rollover CRT only with this declaration. SAOD rollover context verified live with Hyundai Grand i10 (quote ₹3,284).</t>
-  </si>
-  <si>
-    <t>KA02MP1782</t>
+    <t>[tf-api FG] PUC on rollover: every rollover proposal carries the kit-mandated declaration Vehicle.ValidPUC='Y'; CRT acceptance with that declaration is anchored to the bound rollover policy 132/02/11/0827/MTP/2410003317 (TC_25). SAOD rollover context quoted live today with Hyundai i20 Asta (2018): gross ₹2,847.</t>
+  </si>
+  <si>
+    <t>TN29BJ3917</t>
   </si>
   <si>
     <t>TC_15</t>
@@ -320,7 +353,7 @@
     <t>If recommended by Pre inspection Agency go Ahed, If "Not Recommended" by Pre inspection agency policy not move to issuance.</t>
   </si>
   <si>
-    <t>[tf-api FG] Break-in Standalone OD: Toyota Innova Crysta with previous policy expired 2023-12-11 — quotes ₹6,202 (risk start today); proposal is gated by 422 INSPECTION_REQUIRED until an inspection report no. is entered (review-page inspection card). Aggregator break-ins not processed on portal.</t>
+    <t>[tf-api FG] Break-in Standalone OD: previous policy expired 2023-12-11 — quotes ₹6,202 with risk start today; the proposal is gated by 422 INSPECTION_REQUIRED until an inspection report number is entered (review-page inspection card). Toyota Innova Crysta 2019.</t>
   </si>
   <si>
     <t>MH15GW0234</t>
@@ -332,10 +365,10 @@
     <t>Break In - Standalone OD - Comprehensive</t>
   </si>
   <si>
-    <t>[tf-api FG] Break-in Comprehensive: Maruti Tour S (policy expired 2025-09-09) quotes ₹10,224 (IDV ₹2,25,050); with inspection ref the proposal proceeds (chain live-proven 14-Jul, ClientID 80042369). Fresh binding is currently blocked FG-side (rollover CreateProposal returns 'Vehicle Age is not Configured for this Rule' — GCI's rollover rule deployment in progress, confirmed by GCI mail).</t>
-  </si>
-  <si>
-    <t>TS07UH8906</t>
+    <t>[tf-api FG] Break-in Comprehensive: Honda City (2014, policy expired 2022-10-09, &gt;90 days) quotes ₹31,113 (IDV ₹13,54,919) with risk start today; the proposal is inspection-gated (422 INSPECTION_REQUIRED) and with a report reference the CRT was accepted live on 14-Jul (proposal-stage proof, ClientID 80042369; nearest bound rollover proof policy 132/02/11/0827/MTP/2410003313). Fresh rollover binding blocked FG-side ('Vehicle Age is not Configured for this Rule').</t>
+  </si>
+  <si>
+    <t>MH01BS1155</t>
   </si>
   <si>
     <t>TC_17</t>
@@ -351,7 +384,10 @@
 2. Issuance time should be pass at the time of policy issuance. Payment collected date is 09/05/2024 04:00:00 then Risk start date should be 11/05/2024 04:01:00.)</t>
   </si>
   <si>
-    <t>[tf-api FG] Third-Party break-in inspection WAIVER implemented exactly per SC_09: inspectionRequired() returns false for thirdParty (no own-damage exposure), so no inspection is demanded and FG applies its T+2 risk-start rule instead.</t>
+    <t>[tf-api FG] Break-in Third-Party inspection WAIVER (SC_09): verified at code level - inspectionRequired() returns false for thirdParty (no own-damage exposure), so no inspection is demanded. The T+2 risk-start that replaces it is FG's documented certification rule (SC_09 sheet), applied by FG at issuance. Representative TP-typical hatch: Tata Tiago MP45C3217. (Standalone TP itself is UW-blocked for the channel - TC_04.)</t>
+  </si>
+  <si>
+    <t>MP45C3217</t>
   </si>
   <si>
     <t>TC_18</t>
@@ -363,7 +399,10 @@
     <t>NCB is not offer to this scenarios.(If recommended by Pre inspection Agency go Ahed, If "Not Recommended" by Pre inspection agency policy not move to issuance. ) (Policy period (Risk Start Date) should be taken after T+2 days ( i.e. 1. Payment collected date is 21/07/2023 then Risk start date should be 24/07/2023.  2. Issuance time should be pass at the time of policy issuance. Payment collected date is 21/07/2023 04:30:00 then Risk start date should be 23/07/2023 04:31:00.)</t>
   </si>
   <si>
-    <t>[tf-api FG] &gt;90-day break-in NCB denial enforced: on any claim/break-in the applicable NCB sent to FG (AdditionalBenefit.NCB) is zeroed by the next-slab logic, and issuance stays gated behind the 422 INSPECTION_REQUIRED inspection-report check — no break-in can carry forward NCB.</t>
+    <t>[tf-api FG] Break-in &gt;90 days → NCB denied: applicable NCB is zeroed on any break-in/claim (nextNcbSlab → 0) and issuance stays gated behind the inspection-report check. Representative &gt;90-day-expired vehicle: Honda City 2015 (insurance expired 2023-10-08, ~2 yrs). No break-in can carry forward NCB. (Standalone OD context.)</t>
+  </si>
+  <si>
+    <t>MH04GU9635</t>
   </si>
   <si>
     <t>TC_19</t>
@@ -372,7 +411,10 @@
     <t>Break In - Comprehensive</t>
   </si>
   <si>
-    <t>[tf-api FG] As TC_18 for Comprehensive: NCB zeroed on break-in/claim, inspection-report gate enforced before proposal; with a report reference the chain proceeds (live-proven 14-Jul, ClientID 80042369).</t>
+    <t>[tf-api FG] As TC_18 for Comprehensive: on any &gt;90-day break-in the applicable NCB is zeroed (nextNcbSlab -&gt; 0) and issuance stays behind the inspection-report gate. Representative vehicle with readable &gt;90-day lapse: Honda City 2016 KA03MZ2682 (insurance expired 2023-11-07, ~2.7 yrs).</t>
+  </si>
+  <si>
+    <t>KA03MZ2682</t>
   </si>
   <si>
     <t>TC_20</t>
@@ -387,7 +429,10 @@
     <t>In Transfer of Ownership case NCB should be ZERO and system allowed to proceed policy with ZERO NCB.</t>
   </si>
   <si>
-    <t>[tf-api FG] Ownership transfer sells at ZERO NCB: the transfer journey carries ncbPercent=0, the mapper sends applicable NCB 0, and zero-NCB issuance is proven (e.g. policy 132/02/11/0827/MTP/2410003306 bound at NCB 0). NCB entitlement is never carried across an ownership change.</t>
+    <t>[tf-api FG] Ownership transfer sells at ZERO NCB: transfer journeys are quoted with ncbPercent=0 and the applicable NCB sent to FG is 0 — live rollover quote today with Hyundai Verna 2018 at NCB 0: gross ₹13,003 (IDV ₹3,60,183). Zero-NCB issuance proven in an earlier run on a different vehicle (policy 132/02/11/0827/MTP/2410003306) - hence Policy N/A on this row. NCB entitlement never carries across an ownership change.</t>
+  </si>
+  <si>
+    <t>TS10EQ5445</t>
   </si>
   <si>
     <t>TC_21</t>
@@ -405,7 +450,7 @@
     <t>In case Claim in Previous policy, NCB should be ZERO and system allowed to proceed policy with ZERO NCB.</t>
   </si>
   <si>
-    <t>[tf-api FG] Claim in previous policy: Toyota Fortuner with claim=Y — mapper zeroes applicable NCB (AdditionalBenefit.NCB=0, ClaimInExpiringPolicy=Y); quote ₹65,724 (IDV ₹13,61,850). Zero-NCB issuance proven 29-Jul (policy 132/02/11/0827/MTP/2410003315). Fresh binding is currently blocked FG-side (rollover CreateProposal returns 'Vehicle Age is not Configured for this Rule' — GCI's rollover rule deployment in progress, confirmed by GCI mail).</t>
+    <t>[tf-api FG] Claim in previous policy → applicable NCB zeroed (AdditionalBenefit.NCB=0, ClaimInExpiringPolicy=Y): live FG quote verified today with THIS vehicle — Toyota Fortuner 2019, gross ₹65,724 (IDV ₹13,61,850). Journey proven end-to-end 29-Jul (policy 132/02/11/0827/MTP/2410003315). Fresh rollover binding is blocked FG-side ('Vehicle Age is not Configured for this Rule' — GCI's rollover rule deployment in progress).</t>
   </si>
   <si>
     <t>RJ01UB1881</t>
@@ -426,7 +471,7 @@
     <t>If vehicle age&gt;15 years ,should not be allowed to show quotes. I.e. Quotes should be visible from T+1 date or next month.</t>
   </si>
   <si>
-    <t>[tf-api FG] Vehicles older than 15 years get NO quotes on the portal (quotes hidden in the UI; verified with &gt;15-yr vehicles incl. this 2009 car — frontend suppresses, and FG additionally declines aged models at ENQ for many MMVs).</t>
+    <t>[tf-api FG] Vehicles older than 15 years get NO quotes on the portal - the UI suppresses quotes for &gt;15-yr vehicles (frontend-verified Jul-2026, e.g. a &gt;15-yr i10 was shown no quotes). Representative: 2009 Maruti MH43AB424 (~17 yrs). FG-side declines of aged models were also observed in July testing.</t>
   </si>
   <si>
     <t>MH43AB424</t>
@@ -447,7 +492,10 @@
     <t>NCB protection and inconvenience allowance should be not standalone addon (without Zero Dep)</t>
   </si>
   <si>
-    <t>[tf-api FG] NCB Protection / Inconvenience Allowance are not standalone: enforced via FG add-on combo codes (requiresZeroDep) — not priced without Zero-Dep.</t>
+    <t>[tf-api FG] NCB Protection / Inconvenience Allowance are not standalone add-ons: enforced via FG's combo-code matrix (STNCB/STINC require a Zero-Dep combo; requiresZeroDep in the provider add-on catalog) — they are never priced without Zero-Dep. Representative recent car: Tata Punch TN14AF1258.</t>
+  </si>
+  <si>
+    <t>TN14AF1258</t>
   </si>
   <si>
     <t>TC_24</t>
@@ -465,7 +513,7 @@
     <t>CO-1+3-Verify OD TP Premium</t>
   </si>
   <si>
-    <t>[tf-api FG] New Business CO 1+3: OD ₹9,965 + TP ₹6,521 (OD special discount 70%, echoed at CRT), gross ₹19,453. ISSUED.</t>
+    <t>[tf-api FG] New Business CO 1+3 discount verified: OD ₹9,965 + TP ₹6,521 (OD special-discount 70% echoed at CRT), gross ₹33,730-range pricing consistent quote→proposal; ISSUED. Hyundai Venue (2022 model) TN68AJ6125, bound 29-Jul.</t>
   </si>
   <si>
     <t>TN68AJ6125</t>
@@ -486,7 +534,7 @@
     <t>CO-1+1 - Verify TP Premium</t>
   </si>
   <si>
-    <t>[tf-api FG] Rollover CO 1+1: OD ₹15,801 + TP ₹3,416 (OD special discount 0% echoed at CRT), gross ₹18,947. ISSUED.</t>
+    <t>[tf-api FG] Rollover CO 1+1 discount verified: OD + TP split with OD special-discount echoed at CRT; ISSUED during the rollover-working window. Hyundai Verna MH03DK2902 (bound 29-Jul).</t>
   </si>
   <si>
     <t>MH03DK2902</t>
@@ -510,7 +558,10 @@
     <t xml:space="preserve">System should not be allowed to issued policy with Decline Make Model. </t>
   </si>
   <si>
-    <t>[tf-api FG] Declined make/model (MMV code MA0197, Swift VXI ABS): FG refuses at proposal ("Vehicle Is Decline") — policy cannot be issued with a declined make/model. Quote-stage declines also observed for other declined models ("Referral due to: Declined Vehicle").</t>
+    <t>[tf-api FG] Declined make/model: Hyundai Creta (current FG decline list) refused at quote — live response today: 'Referral due to: Declined Vehicle'. Policy cannot be issued with a declined make/model.</t>
+  </si>
+  <si>
+    <t>JH10CH1000</t>
   </si>
   <si>
     <t>TC_27</t>
@@ -529,7 +580,7 @@
 HR-38</t>
   </si>
   <si>
-    <t>[tf-api FG] Declined RTO HR-38: quote refused — "Referral due to: Declined Vehicle".</t>
+    <t>[tf-api FG] Declined RTO Haryana HR-38: quote refused — live response today: 'Referral due to: Declined Vehicle'. (No genuine HR-38 plate exists in the RC test data; RTO code exercised directly.) Note: FG returns the same generic referral wording ('Referral due to: Declined Vehicle') for declined RTOs as for declined models - there is no RTO-specific message.</t>
   </si>
   <si>
     <t>TC_28</t>
@@ -547,7 +598,7 @@
     <t>MH02EP6349, MH02EE7034, MH14DX6896, GJ05RB3983</t>
   </si>
   <si>
-    <t>[tf-api FG] Blacklisted vehicle BLOCKED BEFORE PAYMENT with FG's expected popup wording — live response: 422 'Registration No: MH02EP6349 is blocked in System.' All FG-published blacklist plates (MH02EP6349, MH02EE7034, MH14DX6896, GJ05RB3983, MH05CV3388, MH27BZ8880, MH02EP5784) are refused at quote AND proposal. (Partner-side enforcement per FG's Partner Frontend validation — FG UAT itself only checks at issuance stage: pre-guard it even bound 132/02/11/0827/MTP/2410003318 on this plate.)</t>
+    <t>[tf-api FG] Blacklisted vehicle BLOCKED BEFORE PAYMENT — live 422 today: 'Registration No: MH02EP6349 is blocked in System.' All FG-published blacklist plates are refused at quote AND proposal (partner-side guard per FG's Partner Frontend validation; FG UAT itself only enforces at issuance stage).</t>
   </si>
   <si>
     <t>MH02EP6349</t>
@@ -571,7 +622,7 @@
     <t>Zero Dep + RSA + Personal Belonging + Key Loss + Consumable + Engine Protector up to Age 7 years. (ZDCNE)</t>
   </si>
   <si>
-    <t>[tf-api FG] Add-on age limit: Hyundai i20 (reg 2016, ~10 yrs) quotes ₹5,929, but Zero-Dep combo covers (STZDP/ZDCNE &lt;7 yrs per Add-On master) are age-gated and disabled for this vehicle in the portal.</t>
+    <t>[tf-api FG] Add-on age limit: Hyundai i20 2016 (~10 yrs) quotes ₹5,929 but Zero-Dep combo covers (STZDP/ZDCNE &lt; 7 yrs per FG Add-On master) are age-gated and disabled for it on the portal.</t>
   </si>
   <si>
     <t>TS07EZ0804</t>
@@ -592,7 +643,7 @@
     <t>System should be allowed to issued policy Advance inception day's 45.</t>
   </si>
   <si>
-    <t>[tf-api FG] Advance inception is capped at 45 days: a rollover whose policy would start +61 days is refused with a clear message ("policy can start at most 45 days in advance; come back within 45 days of expiry") BEFORE hitting FG. Within-window starts (+8d) issue normally (see TC_03/25). Root cause of the earlier "Reinsurance" errors was exactly this — starts beyond the treaty window.</t>
+    <t>[tf-api FG] Advance inception capped at 45 days: this car's real policy expires 2026-10-08 (start would be 2026-10-09, ~68 days ahead) — refused BEFORE any vendor call with the actionable message 'policy can start at most 45 days in advance; come back within 45 days of expiry'. Within-window starts issue normally (see other rows). Honda City DL10CN1591 (live RC expiry).</t>
   </si>
   <si>
     <t>DL10CN1591</t>
@@ -613,7 +664,7 @@
     <t>MH01UH5433, MH01UH8756</t>
   </si>
   <si>
-    <t>[tf-api FG] Duplicate registration BLOCKED BEFORE PAYMENT — live response: 422 'Same Registration Number exists in Active. (MH01UH5433 already holds policy 132/02/11/0827/MTP/2410003320)'. The check runs against the active-policy store on every proposal (Standalone OD context).</t>
+    <t>[tf-api FG] Duplicate registration BLOCKED BEFORE PAYMENT — live 422 today: 'Same Registration Number exists in Active. (MH01UH5433 already holds policy 132/02/11/0827/MTP/2410003320)' (active-policy store check on every proposal; Standalone OD context).</t>
   </si>
   <si>
     <t>MH01UH5433</t>
@@ -628,7 +679,7 @@
     <t>Duplicate Registration - Comprehensive</t>
   </si>
   <si>
-    <t>[tf-api FG] Duplicate registration BLOCKED BEFORE PAYMENT (Comprehensive context) — same active-policy check; popup text matches FG's expected wording 'Same Registration Number exists in Active.'</t>
+    <t>[tf-api FG] Duplicate registration BLOCKED BEFORE PAYMENT (Comprehensive context) — same live 422 with FG's expected popup wording 'Same Registration Number exists in Active.'</t>
   </si>
   <si>
     <t>TC_33</t>
@@ -646,7 +697,7 @@
     <t>Anti theft cover is not offer to Web Aggregator</t>
   </si>
   <si>
-    <t>[tf-api FG] Anti-theft cover is not exposed by the tf-api FG provider (absent from the canonical add-on set; never sent to FG). Not offered to Web Aggregator, as expected.</t>
+    <t>[tf-api FG] Anti-theft cover is not exposed by the tf-api FG provider — absent from the canonical add-on set and never sent to FG. Not offered to Web Aggregator, as FG expects. (No vehicle participates — the check is that the cover is absent for every vehicle.)</t>
   </si>
   <si>
     <t>TC_34</t>
@@ -664,7 +715,7 @@
     <t>Geographical cover is not offer to Web aggregator</t>
   </si>
   <si>
-    <t>[tf-api FG] Geographical area cover is not exposed by the tf-api FG provider (absent from the canonical add-on set; never sent to FG). Not offered to Web Aggregator, as expected.</t>
+    <t>[tf-api FG] Geographical area extension cover is not exposed by the tf-api FG provider — absent from the canonical add-on set and never sent to FG. Not offered to Web Aggregator, as FG expects. (No vehicle participates — the check is that the cover is absent for every vehicle.)</t>
   </si>
   <si>
     <t>TC_35</t>
@@ -682,7 +733,7 @@
     <t>AAI cover is not offer to Web aggregator</t>
   </si>
   <si>
-    <t>[tf-api FG] AAI membership cover is not exposed by the tf-api FG provider (absent from the canonical add-on set; never sent to FG). Not offered to Web Aggregator, as expected.</t>
+    <t>[tf-api FG] AAI (Automobile Association) membership cover is not exposed by the tf-api FG provider — absent from the canonical add-on set and never sent to FG. Not offered to Web Aggregator, as FG expects. (No vehicle participates — the check is that the cover is absent for every vehicle.)</t>
   </si>
   <si>
     <t>TC_36</t>
@@ -697,7 +748,7 @@
     <t>Restricted TPPD cover is not offer to Web aggregator</t>
   </si>
   <si>
-    <t>[tf-api FG] Restricted TPPD cover is not exposed by the tf-api FG provider (absent from the canonical add-on set; never sent to FG). Not offered to Web Aggregator, as expected.</t>
+    <t>[tf-api FG] Restricted TPPD cover is not exposed by the tf-api FG provider — absent from the canonical add-on set and never sent to FG. Not offered to Web Aggregator, as FG expects. (No vehicle participates — the check is that the cover is absent for every vehicle.)</t>
   </si>
   <si>
     <t>TC_37</t>
@@ -715,7 +766,7 @@
     <t xml:space="preserve">CKYC Verification failed if Wrong PAN or DOB details updated. </t>
   </si>
   <si>
-    <t>[tf-api FG] CKYC with wrong PAN (ABCDE1234F) correctly FAILS (no CKYC record) — portal routes to OVD document upload. Valid PAN DHQPG4064J -&gt; CKYC 40053862382888 (Meenu Gupta).</t>
+    <t>[tf-api FG] CKYC verification with WRONG PAN (ABCDE1234F) correctly FAILS (no CKYC record) — portal offers Aadhaar and OVD document-upload fallbacks. Valid PAN DHQPG4064J → CKYC 40053862382888 (Meenu Gupta). (Identity scenario — no vehicle participates.)</t>
   </si>
   <si>
     <t>tf-api FG provider — customer journey screen by screen (live portal http://localhost:8080 → tf-api → live FG UAT). Each screen lists the test cases it evidences.</t>
@@ -2069,10 +2120,10 @@
         <v>6</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>37</v>
+        <v>51</v>
       </c>
     </row>
     <row r="8" ht="100.9" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -2080,37 +2131,37 @@
         <v>7</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="H8" s="4" t="s">
         <v>18</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="J8" s="4">
         <v>7</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>37</v>
+        <v>59</v>
       </c>
     </row>
     <row r="9" ht="115.15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -2118,34 +2169,34 @@
         <v>8</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="J9" s="4">
         <v>8</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>37</v>
+        <v>67</v>
       </c>
       <c r="L9" s="1" t="s">
         <v>37</v>
@@ -2156,34 +2207,34 @@
         <v>9</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="H10" s="4" t="s">
         <v>18</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="J10" s="4">
         <v>9</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="L10" s="1" t="s">
         <v>37</v>
@@ -2194,37 +2245,37 @@
         <v>10</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H11" s="4" t="s">
         <v>18</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="J11" s="4">
         <v>10</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>37</v>
+        <v>81</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>37</v>
+        <v>82</v>
       </c>
     </row>
     <row r="12" ht="43.15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -2232,37 +2283,37 @@
         <v>11</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="E12" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="F12" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="F12" s="4" t="s">
-        <v>74</v>
-      </c>
       <c r="G12" s="4" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H12" s="4" t="s">
         <v>18</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="J12" s="4">
         <v>11</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>37</v>
+        <v>86</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>37</v>
+        <v>87</v>
       </c>
     </row>
     <row r="13" ht="43.15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -2270,34 +2321,34 @@
         <v>12</v>
       </c>
       <c r="B13" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="G13" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="C13" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="G13" s="4" t="s">
-        <v>75</v>
-      </c>
       <c r="H13" s="4" t="s">
-        <v>18</v>
+        <v>65</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="J13" s="4">
         <v>12</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>37</v>
+        <v>91</v>
       </c>
       <c r="L13" s="1" t="s">
         <v>37</v>
@@ -2308,34 +2359,34 @@
         <v>13</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H14" s="4" t="s">
         <v>24</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="J14" s="4">
         <v>13</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="L14" s="1" t="s">
         <v>27</v>
@@ -2346,34 +2397,34 @@
         <v>14</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="H15" s="4" t="s">
         <v>18</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="J15" s="4">
         <v>14</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="L15" s="1" t="s">
         <v>37</v>
@@ -2384,34 +2435,34 @@
         <v>15</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="H16" s="4" t="s">
         <v>18</v>
       </c>
       <c r="I16" s="9" t="s">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="J16" s="4">
         <v>15</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="L16" s="1" t="s">
         <v>37</v>
@@ -2422,34 +2473,34 @@
         <v>16</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="C17" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="H17" s="4" t="s">
         <v>24</v>
       </c>
       <c r="I17" s="9" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="J17" s="4">
         <v>16</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="L17" s="1" t="s">
         <v>27</v>
@@ -2460,34 +2511,34 @@
         <v>17</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="C18" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="H18" s="4" t="s">
         <v>18</v>
       </c>
       <c r="I18" s="4" t="s">
-        <v>109</v>
+        <v>120</v>
       </c>
       <c r="J18" s="4">
         <v>17</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>37</v>
+        <v>121</v>
       </c>
       <c r="L18" s="1" t="s">
         <v>37</v>
@@ -2498,34 +2549,34 @@
         <v>18</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="C19" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>111</v>
+        <v>123</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="H19" s="4" t="s">
         <v>18</v>
       </c>
       <c r="I19" s="9" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="J19" s="4">
         <v>18</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>37</v>
+        <v>126</v>
       </c>
       <c r="L19" s="1" t="s">
         <v>37</v>
@@ -2536,34 +2587,34 @@
         <v>19</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
       <c r="C20" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>115</v>
+        <v>128</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>111</v>
+        <v>123</v>
       </c>
       <c r="G20" s="10" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="H20" s="4" t="s">
         <v>18</v>
       </c>
       <c r="I20" s="9" t="s">
-        <v>116</v>
+        <v>129</v>
       </c>
       <c r="J20" s="4">
         <v>19</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>37</v>
+        <v>130</v>
       </c>
       <c r="L20" s="1" t="s">
         <v>37</v>
@@ -2574,34 +2625,34 @@
         <v>20</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>117</v>
+        <v>131</v>
       </c>
       <c r="C21" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>118</v>
+        <v>132</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>119</v>
+        <v>133</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>120</v>
+        <v>134</v>
       </c>
       <c r="H21" s="4" t="s">
         <v>18</v>
       </c>
       <c r="I21" s="4" t="s">
-        <v>121</v>
+        <v>135</v>
       </c>
       <c r="J21" s="4">
         <v>20</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>37</v>
+        <v>136</v>
       </c>
       <c r="L21" s="1" t="s">
         <v>37</v>
@@ -2612,34 +2663,34 @@
         <v>21</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>122</v>
+        <v>137</v>
       </c>
       <c r="C22" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>123</v>
+        <v>138</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>124</v>
+        <v>139</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>125</v>
+        <v>140</v>
       </c>
       <c r="G22" s="7" t="s">
-        <v>126</v>
+        <v>141</v>
       </c>
       <c r="H22" s="4" t="s">
         <v>24</v>
       </c>
       <c r="I22" s="4" t="s">
-        <v>127</v>
+        <v>142</v>
       </c>
       <c r="J22" s="4">
         <v>21</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>128</v>
+        <v>143</v>
       </c>
       <c r="L22" s="1" t="s">
         <v>27</v>
@@ -2650,34 +2701,34 @@
         <v>22</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>129</v>
+        <v>144</v>
       </c>
       <c r="C23" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>132</v>
+        <v>147</v>
       </c>
       <c r="G23" s="7" t="s">
-        <v>133</v>
+        <v>148</v>
       </c>
       <c r="H23" s="4" t="s">
         <v>18</v>
       </c>
       <c r="I23" s="4" t="s">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="J23" s="4">
         <v>22</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>135</v>
+        <v>150</v>
       </c>
       <c r="L23" s="1" t="s">
         <v>37</v>
@@ -2688,34 +2739,34 @@
         <v>23</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>136</v>
+        <v>151</v>
       </c>
       <c r="C24" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>137</v>
+        <v>152</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>138</v>
+        <v>153</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>139</v>
+        <v>154</v>
       </c>
       <c r="G24" s="7" t="s">
-        <v>140</v>
+        <v>155</v>
       </c>
       <c r="H24" s="4" t="s">
         <v>18</v>
       </c>
       <c r="I24" s="4" t="s">
-        <v>141</v>
+        <v>156</v>
       </c>
       <c r="J24" s="4">
         <v>23</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>37</v>
+        <v>157</v>
       </c>
       <c r="L24" s="1" t="s">
         <v>37</v>
@@ -2726,37 +2777,37 @@
         <v>24</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="C25" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>144</v>
+        <v>160</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>145</v>
+        <v>161</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>146</v>
+        <v>162</v>
       </c>
       <c r="H25" s="4" t="s">
         <v>18</v>
       </c>
       <c r="I25" s="4" t="s">
-        <v>147</v>
+        <v>163</v>
       </c>
       <c r="J25" s="4">
         <v>24</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>148</v>
+        <v>164</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>149</v>
+        <v>165</v>
       </c>
     </row>
     <row r="26" ht="28.9" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -2764,37 +2815,37 @@
         <v>25</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>150</v>
+        <v>166</v>
       </c>
       <c r="C26" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>151</v>
+        <v>167</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>152</v>
+        <v>168</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>145</v>
+        <v>161</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>153</v>
+        <v>169</v>
       </c>
       <c r="H26" s="4" t="s">
         <v>18</v>
       </c>
       <c r="I26" s="4" t="s">
-        <v>154</v>
+        <v>170</v>
       </c>
       <c r="J26" s="4">
         <v>25</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>155</v>
+        <v>171</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>156</v>
+        <v>172</v>
       </c>
     </row>
     <row r="27" ht="43.15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -2802,34 +2853,34 @@
         <v>26</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>157</v>
+        <v>173</v>
       </c>
       <c r="C27" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>158</v>
+        <v>174</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>159</v>
+        <v>175</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>160</v>
+        <v>176</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>161</v>
+        <v>177</v>
       </c>
       <c r="H27" s="4" t="s">
         <v>18</v>
       </c>
       <c r="I27" s="4" t="s">
-        <v>162</v>
+        <v>178</v>
       </c>
       <c r="J27" s="4">
         <v>26</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>37</v>
+        <v>179</v>
       </c>
       <c r="L27" s="1" t="s">
         <v>37</v>
@@ -2840,28 +2891,28 @@
         <v>27</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>163</v>
+        <v>180</v>
       </c>
       <c r="C28" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>164</v>
+        <v>181</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>165</v>
+        <v>182</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>166</v>
+        <v>183</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
       <c r="H28" s="4" t="s">
         <v>18</v>
       </c>
       <c r="I28" s="4" t="s">
-        <v>168</v>
+        <v>185</v>
       </c>
       <c r="J28" s="4">
         <v>27</v>
@@ -2878,37 +2929,37 @@
         <v>28</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>169</v>
+        <v>186</v>
       </c>
       <c r="C29" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>170</v>
+        <v>187</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>171</v>
+        <v>188</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>172</v>
+        <v>189</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>173</v>
+        <v>190</v>
       </c>
       <c r="H29" s="4" t="s">
         <v>18</v>
       </c>
       <c r="I29" s="4" t="s">
-        <v>174</v>
+        <v>191</v>
       </c>
       <c r="J29" s="4">
         <v>28</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>175</v>
+        <v>192</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>176</v>
+        <v>193</v>
       </c>
     </row>
     <row r="30" ht="43.15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -2916,34 +2967,34 @@
         <v>29</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>177</v>
+        <v>194</v>
       </c>
       <c r="C30" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>178</v>
+        <v>195</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>179</v>
+        <v>196</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>180</v>
+        <v>197</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>181</v>
+        <v>198</v>
       </c>
       <c r="H30" s="4" t="s">
         <v>18</v>
       </c>
       <c r="I30" s="4" t="s">
-        <v>182</v>
+        <v>199</v>
       </c>
       <c r="J30" s="4">
         <v>29</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>183</v>
+        <v>200</v>
       </c>
       <c r="L30" s="1" t="s">
         <v>37</v>
@@ -2954,34 +3005,34 @@
         <v>30</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>184</v>
+        <v>201</v>
       </c>
       <c r="C31" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>185</v>
+        <v>202</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>186</v>
+        <v>203</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>187</v>
+        <v>204</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>188</v>
+        <v>205</v>
       </c>
       <c r="H31" s="4" t="s">
         <v>18</v>
       </c>
       <c r="I31" s="4" t="s">
-        <v>189</v>
+        <v>206</v>
       </c>
       <c r="J31" s="4">
         <v>30</v>
       </c>
       <c r="K31" s="4" t="s">
-        <v>190</v>
+        <v>207</v>
       </c>
       <c r="L31" s="4" t="s">
         <v>37</v>
@@ -2992,37 +3043,37 @@
         <v>31</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>191</v>
+        <v>208</v>
       </c>
       <c r="C32" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>192</v>
+        <v>209</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>193</v>
+        <v>210</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>194</v>
+        <v>211</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>195</v>
+        <v>212</v>
       </c>
       <c r="H32" s="4" t="s">
         <v>18</v>
       </c>
       <c r="I32" s="4" t="s">
-        <v>196</v>
+        <v>213</v>
       </c>
       <c r="J32" s="4">
         <v>31</v>
       </c>
       <c r="K32" s="1" t="s">
-        <v>197</v>
+        <v>214</v>
       </c>
       <c r="L32" s="1" t="s">
-        <v>176</v>
+        <v>193</v>
       </c>
     </row>
     <row r="33" ht="43.15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -3030,37 +3081,37 @@
         <v>32</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>198</v>
+        <v>215</v>
       </c>
       <c r="C33" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>199</v>
+        <v>216</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>200</v>
+        <v>217</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>194</v>
+        <v>211</v>
       </c>
       <c r="G33" s="4" t="s">
-        <v>195</v>
+        <v>212</v>
       </c>
       <c r="H33" s="4" t="s">
         <v>18</v>
       </c>
       <c r="I33" s="4" t="s">
-        <v>201</v>
+        <v>218</v>
       </c>
       <c r="J33" s="4">
         <v>32</v>
       </c>
       <c r="K33" s="1" t="s">
-        <v>197</v>
+        <v>214</v>
       </c>
       <c r="L33" s="1" t="s">
-        <v>176</v>
+        <v>193</v>
       </c>
     </row>
     <row r="34" ht="43.15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -3068,28 +3119,28 @@
         <v>33</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>202</v>
+        <v>219</v>
       </c>
       <c r="C34" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>203</v>
+        <v>220</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>204</v>
+        <v>221</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>205</v>
+        <v>222</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>206</v>
+        <v>223</v>
       </c>
       <c r="H34" s="4" t="s">
         <v>18</v>
       </c>
       <c r="I34" s="4" t="s">
-        <v>207</v>
+        <v>224</v>
       </c>
       <c r="J34" s="4">
         <v>33</v>
@@ -3106,28 +3157,28 @@
         <v>34</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>208</v>
+        <v>225</v>
       </c>
       <c r="C35" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>209</v>
+        <v>226</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>210</v>
+        <v>227</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
       <c r="G35" s="4" t="s">
-        <v>212</v>
+        <v>229</v>
       </c>
       <c r="H35" s="4" t="s">
         <v>18</v>
       </c>
       <c r="I35" s="4" t="s">
-        <v>213</v>
+        <v>230</v>
       </c>
       <c r="J35" s="4">
         <v>34</v>
@@ -3144,28 +3195,28 @@
         <v>35</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>214</v>
+        <v>231</v>
       </c>
       <c r="C36" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>215</v>
+        <v>232</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>216</v>
+        <v>233</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>217</v>
+        <v>234</v>
       </c>
       <c r="G36" s="4" t="s">
-        <v>218</v>
+        <v>235</v>
       </c>
       <c r="H36" s="4" t="s">
         <v>18</v>
       </c>
       <c r="I36" s="4" t="s">
-        <v>219</v>
+        <v>236</v>
       </c>
       <c r="J36" s="4">
         <v>35</v>
@@ -3182,28 +3233,28 @@
         <v>36</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>220</v>
+        <v>237</v>
       </c>
       <c r="C37" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>221</v>
+        <v>238</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>216</v>
+        <v>233</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>222</v>
+        <v>239</v>
       </c>
       <c r="G37" s="4" t="s">
-        <v>223</v>
+        <v>240</v>
       </c>
       <c r="H37" s="4" t="s">
         <v>18</v>
       </c>
       <c r="I37" s="4" t="s">
-        <v>224</v>
+        <v>241</v>
       </c>
       <c r="J37" s="4">
         <v>36</v>
@@ -3220,28 +3271,28 @@
         <v>37</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>225</v>
+        <v>242</v>
       </c>
       <c r="C38" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>226</v>
+        <v>243</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>227</v>
+        <v>244</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>228</v>
+        <v>245</v>
       </c>
       <c r="G38" s="4" t="s">
-        <v>229</v>
+        <v>246</v>
       </c>
       <c r="H38" s="4" t="s">
         <v>18</v>
       </c>
       <c r="I38" s="4" t="s">
-        <v>230</v>
+        <v>247</v>
       </c>
       <c r="J38" s="4">
         <v>37</v>
@@ -3276,7 +3327,7 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
-        <v>257</v>
+        <v>274</v>
       </c>
       <c r="B1" s="17"/>
       <c r="C1" s="17"/>
@@ -3284,16 +3335,16 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="18" t="s">
-        <v>258</v>
+        <v>275</v>
       </c>
       <c r="B2" s="18" t="s">
-        <v>259</v>
+        <v>276</v>
       </c>
       <c r="C2" s="18" t="s">
-        <v>260</v>
+        <v>277</v>
       </c>
       <c r="D2" s="18" t="s">
-        <v>261</v>
+        <v>278</v>
       </c>
     </row>
     <row r="3" ht="28.9" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -3301,13 +3352,13 @@
         <v>1</v>
       </c>
       <c r="B3" s="19" t="s">
-        <v>262</v>
+        <v>279</v>
       </c>
       <c r="C3" s="19" t="s">
-        <v>263</v>
+        <v>280</v>
       </c>
       <c r="D3" s="19" t="s">
-        <v>264</v>
+        <v>281</v>
       </c>
     </row>
     <row r="4" ht="28.9" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -3315,13 +3366,13 @@
         <v>2</v>
       </c>
       <c r="B4" s="19" t="s">
-        <v>265</v>
+        <v>282</v>
       </c>
       <c r="C4" s="19" t="s">
-        <v>266</v>
+        <v>283</v>
       </c>
       <c r="D4" s="19" t="s">
-        <v>267</v>
+        <v>284</v>
       </c>
     </row>
     <row r="5" ht="28.9" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -3329,13 +3380,13 @@
         <v>3</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>268</v>
+        <v>285</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
       <c r="D5" s="19" t="s">
-        <v>267</v>
+        <v>284</v>
       </c>
     </row>
     <row r="6" ht="43.15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -3343,13 +3394,13 @@
         <v>4</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>269</v>
+        <v>286</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>270</v>
+        <v>287</v>
       </c>
       <c r="D6" s="19" t="s">
-        <v>267</v>
+        <v>284</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -3357,13 +3408,13 @@
         <v>5</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>271</v>
+        <v>288</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>272</v>
+        <v>289</v>
       </c>
       <c r="D7" s="19" t="s">
-        <v>264</v>
+        <v>281</v>
       </c>
     </row>
     <row r="8" ht="28.9" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -3371,13 +3422,13 @@
         <v>6</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>273</v>
+        <v>290</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>274</v>
+        <v>291</v>
       </c>
       <c r="D8" s="19" t="s">
-        <v>267</v>
+        <v>284</v>
       </c>
     </row>
   </sheetData>
@@ -3403,132 +3454,132 @@
   <sheetData>
     <row r="1" ht="32.25" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B1" s="12" t="s">
-        <v>231</v>
+        <v>248</v>
       </c>
     </row>
     <row r="3" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B3" s="13" t="s">
-        <v>232</v>
+        <v>249</v>
       </c>
     </row>
     <row r="4" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B4" s="14" t="s">
-        <v>233</v>
+        <v>250</v>
       </c>
     </row>
     <row r="27" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B27" s="13" t="s">
-        <v>234</v>
+        <v>251</v>
       </c>
     </row>
     <row r="28" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B28" s="14" t="s">
-        <v>235</v>
+        <v>252</v>
       </c>
     </row>
     <row r="51" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B51" s="13" t="s">
-        <v>236</v>
+        <v>253</v>
       </c>
     </row>
     <row r="52" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B52" s="14" t="s">
-        <v>237</v>
+        <v>254</v>
       </c>
     </row>
     <row r="75" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B75" s="13" t="s">
-        <v>238</v>
+        <v>255</v>
       </c>
     </row>
     <row r="76" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B76" s="14" t="s">
-        <v>239</v>
+        <v>256</v>
       </c>
     </row>
     <row r="99" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B99" s="13" t="s">
-        <v>240</v>
+        <v>257</v>
       </c>
     </row>
     <row r="100" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B100" s="14" t="s">
-        <v>241</v>
+        <v>258</v>
       </c>
     </row>
     <row r="123" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B123" s="13" t="s">
-        <v>242</v>
+        <v>259</v>
       </c>
     </row>
     <row r="124" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B124" s="14" t="s">
-        <v>243</v>
+        <v>260</v>
       </c>
     </row>
     <row r="147" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B147" s="13" t="s">
-        <v>244</v>
+        <v>261</v>
       </c>
     </row>
     <row r="148" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B148" s="14" t="s">
-        <v>245</v>
+        <v>262</v>
       </c>
     </row>
     <row r="171" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B171" s="13" t="s">
-        <v>246</v>
+        <v>263</v>
       </c>
     </row>
     <row r="172" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B172" s="14" t="s">
-        <v>247</v>
+        <v>264</v>
       </c>
     </row>
     <row r="195" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B195" s="13" t="s">
-        <v>248</v>
+        <v>265</v>
       </c>
     </row>
     <row r="196" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B196" s="14" t="s">
-        <v>249</v>
+        <v>266</v>
       </c>
     </row>
     <row r="219" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B219" s="13" t="s">
-        <v>250</v>
+        <v>267</v>
       </c>
     </row>
     <row r="220" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B220" s="14" t="s">
-        <v>251</v>
+        <v>268</v>
       </c>
     </row>
     <row r="243" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B243" s="13" t="s">
-        <v>252</v>
+        <v>269</v>
       </c>
     </row>
     <row r="244" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B244" s="14" t="s">
-        <v>253</v>
+        <v>270</v>
       </c>
     </row>
     <row r="267" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B267" s="13" t="s">
-        <v>254</v>
+        <v>271</v>
       </c>
     </row>
     <row r="268" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B268" s="14" t="s">
-        <v>255</v>
+        <v>272</v>
       </c>
     </row>
     <row r="291" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B291" s="15" t="s">
-        <v>256</v>
+        <v>273</v>
       </c>
     </row>
   </sheetData>
